--- a/ROSA_vitaSPEC/Results/test_pretraitements/ratio.alpha.beta/Resultats_ratio.alpha.beta_moy_RMSEP.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/ratio.alpha.beta/Resultats_ratio.alpha.beta_moy_RMSEP.xlsx
@@ -1,220 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U108-N806\Documents\STAGE_M2_ROSA_NIRS\VitaSPEC\vitaspec_R\ROSA_vitaSPEC\Results\test_pretraitements\ratio.alpha.beta\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
-  <si>
-    <t>Pretraitement</t>
-  </si>
-  <si>
-    <t>RMSEP_glo</t>
-  </si>
-  <si>
-    <t>LV1_RMSEP</t>
-  </si>
-  <si>
-    <t>LV2_RMSEP</t>
-  </si>
-  <si>
-    <t>LV3_RMSEP</t>
-  </si>
-  <si>
-    <t>LV4_RMSEP</t>
-  </si>
-  <si>
-    <t>LV5_RMSEP</t>
-  </si>
-  <si>
-    <t>LV6_RMSEP</t>
-  </si>
-  <si>
-    <t>LV7_RMSEP</t>
-  </si>
-  <si>
-    <t>LV8_RMSEP</t>
-  </si>
-  <si>
-    <t>LV9_RMSEP</t>
-  </si>
-  <si>
-    <t>LV10_RMSEP</t>
-  </si>
-  <si>
-    <t>LV11_RMSEP</t>
-  </si>
-  <si>
-    <t>LV12_RMSEP</t>
-  </si>
-  <si>
-    <t>LV13_RMSEP</t>
-  </si>
-  <si>
-    <t>LV14_RMSEP</t>
-  </si>
-  <si>
-    <t>LV15_RMSEP</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1000,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(1,3,5)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -226,13 +27,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -258,68 +52,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -361,7 +109,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -393,10 +141,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -428,7 +175,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -604,2520 +350,2628 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:Q47"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="51.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="11" width="12" bestFit="1" customWidth="1"/>
-    <col min="12" max="17" width="12.28515625" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>17</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Pretraitement</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>RMSEP_glo</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>LV1_RMSEP</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LV2_RMSEP</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>LV3_RMSEP</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>LV4_RMSEP</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>LV5_RMSEP</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>LV6_RMSEP</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>LV7_RMSEP</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>LV8_RMSEP</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>LV9_RMSEP</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>LV10_RMSEP</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>LV11_RMSEP</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>LV12_RMSEP</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>LV13_RMSEP</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>LV14_RMSEP</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>LV15_RMSEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1000,1)_snv_</t>
+        </is>
       </c>
       <c r="B2">
-        <v>0.4176544742393643</v>
+        <v>0.4226742440226443</v>
       </c>
       <c r="C2">
-        <v>0.48905450109146609</v>
+        <v>0.4888192059822374</v>
       </c>
       <c r="D2">
-        <v>0.49308561454907718</v>
+        <v>0.4939198133694742</v>
       </c>
       <c r="E2">
-        <v>0.49456904204310143</v>
+        <v>0.4954290671558664</v>
       </c>
       <c r="F2">
-        <v>0.49510560073002552</v>
+        <v>0.4961688360137458</v>
       </c>
       <c r="G2">
-        <v>0.49494856900554179</v>
+        <v>0.4947404259449011</v>
       </c>
       <c r="H2">
-        <v>0.49799644021788642</v>
+        <v>0.4971004001245919</v>
       </c>
       <c r="I2">
-        <v>0.4810517514728001</v>
+        <v>0.4826085635895935</v>
       </c>
       <c r="J2">
-        <v>0.45984579908707252</v>
+        <v>0.4606257657292137</v>
       </c>
       <c r="K2">
-        <v>0.4709487784993977</v>
+        <v>0.4698804531704709</v>
       </c>
       <c r="L2">
-        <v>0.46002422566539869</v>
+        <v>0.4611261729777885</v>
       </c>
       <c r="M2">
-        <v>0.43366964648625711</v>
+        <v>0.4358471295989863</v>
       </c>
       <c r="N2">
-        <v>0.42434422656549109</v>
+        <v>0.4268531836722555</v>
       </c>
       <c r="O2">
-        <v>0.40052832202829391</v>
+        <v>0.4024302078339416</v>
       </c>
       <c r="P2">
-        <v>0.37783213906730628</v>
+        <v>0.379546689683589</v>
       </c>
       <c r="Q2">
-        <v>0.36551859550852112</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>18</v>
+        <v>0.3652001878663406</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B3">
-        <v>0.43283005527436769</v>
+        <v>0.4372841819775964</v>
       </c>
       <c r="C3">
-        <v>0.4866442436571341</v>
+        <v>0.4864608223713254</v>
       </c>
       <c r="D3">
-        <v>0.49411894138504198</v>
+        <v>0.4924185240634107</v>
       </c>
       <c r="E3">
-        <v>0.52198932910991724</v>
+        <v>0.5209343838015882</v>
       </c>
       <c r="F3">
-        <v>0.47816626999186618</v>
+        <v>0.4759541854591819</v>
       </c>
       <c r="G3">
-        <v>0.454173571365795</v>
+        <v>0.4511037545581915</v>
       </c>
       <c r="H3">
-        <v>0.43670228046768939</v>
+        <v>0.4373632596191334</v>
       </c>
       <c r="I3">
-        <v>0.42405590956907291</v>
+        <v>0.425696472017711</v>
       </c>
       <c r="J3">
-        <v>0.41768541405995557</v>
+        <v>0.4209984155551564</v>
       </c>
       <c r="K3">
-        <v>0.3982532804399263</v>
+        <v>0.4030933241578818</v>
       </c>
       <c r="L3">
-        <v>0.38542307898079942</v>
+        <v>0.3904016543640056</v>
       </c>
       <c r="M3">
-        <v>0.38645173257494292</v>
+        <v>0.3906610689566032</v>
       </c>
       <c r="N3">
-        <v>0.38387051437759162</v>
+        <v>0.389201213020162</v>
       </c>
       <c r="O3">
-        <v>0.39187481653097589</v>
+        <v>0.3969458648841259</v>
       </c>
       <c r="P3">
-        <v>0.39465685330954142</v>
+        <v>0.3967466845188405</v>
       </c>
       <c r="Q3">
-        <v>0.38794452909009641</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>19</v>
+        <v>0.3893727813626784</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B4">
-        <v>0.42824219213041309</v>
+        <v>0.4288861114333317</v>
       </c>
       <c r="C4">
-        <v>0.48908655181336108</v>
+        <v>0.4895273378388955</v>
       </c>
       <c r="D4">
-        <v>0.49259502939644501</v>
+        <v>0.4920298717348165</v>
       </c>
       <c r="E4">
-        <v>0.51234961508640098</v>
+        <v>0.5099011746786603</v>
       </c>
       <c r="F4">
-        <v>0.51099667485986311</v>
+        <v>0.5083361640715831</v>
       </c>
       <c r="G4">
-        <v>0.52529560873332415</v>
+        <v>0.5218070765171465</v>
       </c>
       <c r="H4">
-        <v>0.49298468260479911</v>
+        <v>0.491004811136202</v>
       </c>
       <c r="I4">
-        <v>0.45892828026583732</v>
+        <v>0.456922466791794</v>
       </c>
       <c r="J4">
-        <v>0.45840095601375952</v>
+        <v>0.4526162010971782</v>
       </c>
       <c r="K4">
-        <v>0.45076244090889073</v>
+        <v>0.4466113847803301</v>
       </c>
       <c r="L4">
-        <v>0.43159949132250153</v>
+        <v>0.4309764779854283</v>
       </c>
       <c r="M4">
-        <v>0.41110293999693892</v>
+        <v>0.4101806487100563</v>
       </c>
       <c r="N4">
-        <v>0.39405431970556332</v>
+        <v>0.3926886297450659</v>
       </c>
       <c r="O4">
-        <v>0.38121450811601582</v>
+        <v>0.3796684462480264</v>
       </c>
       <c r="P4">
-        <v>0.37807574016149892</v>
+        <v>0.3777417201385767</v>
       </c>
       <c r="Q4">
-        <v>0.38106151939430932</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>20</v>
+        <v>0.3788010070208745</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B5">
-        <v>0.39875313697681419</v>
+        <v>0.3965240521093475</v>
       </c>
       <c r="C5">
-        <v>0.48666881012715862</v>
+        <v>0.4868488755834224</v>
       </c>
       <c r="D5">
-        <v>0.49634255654410853</v>
+        <v>0.4989030846696772</v>
       </c>
       <c r="E5">
-        <v>0.49970080948857631</v>
+        <v>0.4991494597594291</v>
       </c>
       <c r="F5">
-        <v>0.5114398903730859</v>
+        <v>0.5113773547258474</v>
       </c>
       <c r="G5">
-        <v>0.45973507759724702</v>
+        <v>0.4595755307192697</v>
       </c>
       <c r="H5">
-        <v>0.43366108262216718</v>
+        <v>0.432034583245052</v>
       </c>
       <c r="I5">
-        <v>0.41944520004448083</v>
+        <v>0.4198513834017426</v>
       </c>
       <c r="J5">
-        <v>0.40369475268524169</v>
+        <v>0.4020968333859172</v>
       </c>
       <c r="K5">
-        <v>0.38223916114260131</v>
+        <v>0.382578168759426</v>
       </c>
       <c r="L5">
-        <v>0.37247196869530141</v>
+        <v>0.3732070544697877</v>
       </c>
       <c r="M5">
-        <v>0.35959647185533378</v>
+        <v>0.3618529093119336</v>
       </c>
       <c r="N5">
-        <v>0.35925285051211631</v>
+        <v>0.3623118425558357</v>
       </c>
       <c r="O5">
-        <v>0.36504257906678877</v>
+        <v>0.3693110305130579</v>
       </c>
       <c r="P5">
-        <v>0.371235912931281</v>
+        <v>0.375602924806527</v>
       </c>
       <c r="Q5">
-        <v>0.37860026004230252</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>21</v>
+        <v>0.3820836641704876</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B6">
-        <v>0.38103440315739212</v>
+        <v>0.3773849962458408</v>
       </c>
       <c r="C6">
-        <v>0.48665165601412352</v>
+        <v>0.4873484012094193</v>
       </c>
       <c r="D6">
-        <v>0.4965267556812375</v>
+        <v>0.4989234372983741</v>
       </c>
       <c r="E6">
-        <v>0.49828577877698438</v>
+        <v>0.4970582673545261</v>
       </c>
       <c r="F6">
-        <v>0.49661026389467439</v>
+        <v>0.4945546835260101</v>
       </c>
       <c r="G6">
-        <v>0.44354788549111562</v>
+        <v>0.4409719097248134</v>
       </c>
       <c r="H6">
-        <v>0.40787755164904937</v>
+        <v>0.404688369015001</v>
       </c>
       <c r="I6">
-        <v>0.39862128338494868</v>
+        <v>0.3915713381815271</v>
       </c>
       <c r="J6">
-        <v>0.374701422068284</v>
+        <v>0.3708316797016893</v>
       </c>
       <c r="K6">
-        <v>0.35998664822563309</v>
+        <v>0.3576917498319881</v>
       </c>
       <c r="L6">
-        <v>0.35330827995181552</v>
+        <v>0.3498784022900627</v>
       </c>
       <c r="M6">
-        <v>0.34801166961173791</v>
+        <v>0.3440611582453303</v>
       </c>
       <c r="N6">
-        <v>0.34537231154792009</v>
+        <v>0.3426460995760416</v>
       </c>
       <c r="O6">
-        <v>0.34767719183092699</v>
+        <v>0.3447274919009714</v>
       </c>
       <c r="P6">
-        <v>0.34505708394696338</v>
+        <v>0.3427312516525445</v>
       </c>
       <c r="Q6">
-        <v>0.35101375018716258</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>22</v>
+        <v>0.3467130054281706</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B7">
-        <v>0.42579324851446848</v>
+        <v>0.4301065386006754</v>
       </c>
       <c r="C7">
-        <v>0.48865605882579533</v>
+        <v>0.4903685148416082</v>
       </c>
       <c r="D7">
-        <v>0.49218931346680878</v>
+        <v>0.4940547294511766</v>
       </c>
       <c r="E7">
-        <v>0.512776387698751</v>
+        <v>0.5147069630665639</v>
       </c>
       <c r="F7">
-        <v>0.51407920695070386</v>
+        <v>0.5165627611452566</v>
       </c>
       <c r="G7">
-        <v>0.52420769625963382</v>
+        <v>0.5269365335468842</v>
       </c>
       <c r="H7">
-        <v>0.52083334772788981</v>
+        <v>0.5240584056348191</v>
       </c>
       <c r="I7">
-        <v>0.48609352125338001</v>
+        <v>0.4877829034660921</v>
       </c>
       <c r="J7">
-        <v>0.4562868707622848</v>
+        <v>0.4578790623974783</v>
       </c>
       <c r="K7">
-        <v>0.45814042674889488</v>
+        <v>0.4577979918215447</v>
       </c>
       <c r="L7">
-        <v>0.44589959349786662</v>
+        <v>0.4477089965404905</v>
       </c>
       <c r="M7">
-        <v>0.42144650099872022</v>
+        <v>0.4246782970642763</v>
       </c>
       <c r="N7">
-        <v>0.40224647424150861</v>
+        <v>0.404253345971022</v>
       </c>
       <c r="O7">
-        <v>0.38768596213322543</v>
+        <v>0.3888965093752614</v>
       </c>
       <c r="P7">
-        <v>0.37840715078108578</v>
+        <v>0.3791835166871299</v>
       </c>
       <c r="Q7">
-        <v>0.37504249986763688</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>23</v>
+        <v>0.3745246469420439</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B8">
-        <v>0.41140766764864928</v>
+        <v>0.4101705403975482</v>
       </c>
       <c r="C8">
-        <v>0.48797350465024891</v>
+        <v>0.4881821792959191</v>
       </c>
       <c r="D8">
-        <v>0.49175948504054728</v>
+        <v>0.4914198781097748</v>
       </c>
       <c r="E8">
-        <v>0.51117832829945542</v>
+        <v>0.5088882716768263</v>
       </c>
       <c r="F8">
-        <v>0.51662047633406227</v>
+        <v>0.5164976949109451</v>
       </c>
       <c r="G8">
-        <v>0.50347909867317109</v>
+        <v>0.5002131556379041</v>
       </c>
       <c r="H8">
-        <v>0.47856763468036961</v>
+        <v>0.4778092685358511</v>
       </c>
       <c r="I8">
-        <v>0.4650070692350084</v>
+        <v>0.46290947884958</v>
       </c>
       <c r="J8">
-        <v>0.4398575446917285</v>
+        <v>0.4390433922451742</v>
       </c>
       <c r="K8">
-        <v>0.42725084964217203</v>
+        <v>0.4264940217581807</v>
       </c>
       <c r="L8">
-        <v>0.39485341077399422</v>
+        <v>0.3941816708605062</v>
       </c>
       <c r="M8">
-        <v>0.39364334019692082</v>
+        <v>0.3900470935716154</v>
       </c>
       <c r="N8">
-        <v>0.37928342541732668</v>
+        <v>0.3767174891348817</v>
       </c>
       <c r="O8">
-        <v>0.36737168960996852</v>
+        <v>0.3648473255507672</v>
       </c>
       <c r="P8">
-        <v>0.3671807148222484</v>
+        <v>0.363716793952643</v>
       </c>
       <c r="Q8">
-        <v>0.36771135334595112</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>24</v>
+        <v>0.3667396287543956</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B9">
-        <v>0.38602613781184031</v>
+        <v>0.3871513585522323</v>
       </c>
       <c r="C9">
-        <v>0.48771063697916828</v>
+        <v>0.487421932026302</v>
       </c>
       <c r="D9">
-        <v>0.49137743444051207</v>
+        <v>0.4905668078456105</v>
       </c>
       <c r="E9">
-        <v>0.50719434763695537</v>
+        <v>0.5075376876647836</v>
       </c>
       <c r="F9">
-        <v>0.51209762162799555</v>
+        <v>0.5115652237231942</v>
       </c>
       <c r="G9">
-        <v>0.49943500389527801</v>
+        <v>0.4996270893921387</v>
       </c>
       <c r="H9">
-        <v>0.47675986277400861</v>
+        <v>0.4764526896287188</v>
       </c>
       <c r="I9">
-        <v>0.46546518154871519</v>
+        <v>0.4620243340064498</v>
       </c>
       <c r="J9">
-        <v>0.43834897048883309</v>
+        <v>0.4378661573001416</v>
       </c>
       <c r="K9">
-        <v>0.42750640722757499</v>
+        <v>0.4273175357086308</v>
       </c>
       <c r="L9">
-        <v>0.38422886189942268</v>
+        <v>0.3836553136211127</v>
       </c>
       <c r="M9">
-        <v>0.38131022816075549</v>
+        <v>0.3789089010751477</v>
       </c>
       <c r="N9">
-        <v>0.36901997482937748</v>
+        <v>0.3678343341588176</v>
       </c>
       <c r="O9">
-        <v>0.35802777811129732</v>
+        <v>0.3574541197324786</v>
       </c>
       <c r="P9">
-        <v>0.35615405348675311</v>
+        <v>0.355509927471088</v>
       </c>
       <c r="Q9">
-        <v>0.3563312593882435</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>25</v>
+        <v>0.3543739906704627</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B10">
-        <v>0.39362372468766937</v>
+        <v>0.392838093299285</v>
       </c>
       <c r="C10">
-        <v>0.48844903321264171</v>
+        <v>0.4882908567812589</v>
       </c>
       <c r="D10">
-        <v>0.49215724958165608</v>
+        <v>0.4920483125289776</v>
       </c>
       <c r="E10">
-        <v>0.5089076542593306</v>
+        <v>0.5083425796290446</v>
       </c>
       <c r="F10">
-        <v>0.5136999840074169</v>
+        <v>0.5120823773685561</v>
       </c>
       <c r="G10">
-        <v>0.50190222488839753</v>
+        <v>0.4991059693850192</v>
       </c>
       <c r="H10">
-        <v>0.47886585674682958</v>
+        <v>0.4798197005524167</v>
       </c>
       <c r="I10">
-        <v>0.46595883649674319</v>
+        <v>0.4658804505790127</v>
       </c>
       <c r="J10">
-        <v>0.43966188637174181</v>
+        <v>0.4404598336859399</v>
       </c>
       <c r="K10">
-        <v>0.43096043793744448</v>
+        <v>0.4298169808290867</v>
       </c>
       <c r="L10">
-        <v>0.38748869085876553</v>
+        <v>0.3860132288424725</v>
       </c>
       <c r="M10">
-        <v>0.38588934737812403</v>
+        <v>0.3854794277952696</v>
       </c>
       <c r="N10">
-        <v>0.37499174308219041</v>
+        <v>0.3730679239704072</v>
       </c>
       <c r="O10">
-        <v>0.36507447235534601</v>
+        <v>0.361386021292406</v>
       </c>
       <c r="P10">
-        <v>0.36316059814710611</v>
+        <v>0.3605391456939658</v>
       </c>
       <c r="Q10">
-        <v>0.36166703082687479</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>26</v>
+        <v>0.3584173634623262</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B11">
-        <v>0.38900618024289008</v>
+        <v>0.3883563894556256</v>
       </c>
       <c r="C11">
-        <v>0.48794512168455101</v>
+        <v>0.4880611176900764</v>
       </c>
       <c r="D11">
-        <v>0.49120232836841721</v>
+        <v>0.4919160922398127</v>
       </c>
       <c r="E11">
-        <v>0.50849360359030638</v>
+        <v>0.5099102285141707</v>
       </c>
       <c r="F11">
-        <v>0.51182542636245654</v>
+        <v>0.5162591525731344</v>
       </c>
       <c r="G11">
-        <v>0.50106045585944103</v>
+        <v>0.504011721519167</v>
       </c>
       <c r="H11">
-        <v>0.47884913172748689</v>
+        <v>0.4781199644904124</v>
       </c>
       <c r="I11">
-        <v>0.46630689353597421</v>
+        <v>0.4677717242929246</v>
       </c>
       <c r="J11">
-        <v>0.44047088543584961</v>
+        <v>0.4405858716358577</v>
       </c>
       <c r="K11">
-        <v>0.43021615466150992</v>
+        <v>0.4293355337053935</v>
       </c>
       <c r="L11">
-        <v>0.3852534098129497</v>
+        <v>0.3838222127954313</v>
       </c>
       <c r="M11">
-        <v>0.38040128437651688</v>
+        <v>0.3800767387107911</v>
       </c>
       <c r="N11">
-        <v>0.3674104026640026</v>
+        <v>0.3674829915440919</v>
       </c>
       <c r="O11">
-        <v>0.35866030322990311</v>
+        <v>0.3577822566691834</v>
       </c>
       <c r="P11">
-        <v>0.35740228815052388</v>
+        <v>0.3576609150351822</v>
       </c>
       <c r="Q11">
-        <v>0.3555543379617554</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>27</v>
+        <v>0.3561003324177224</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B12">
-        <v>0.38734335083066618</v>
+        <v>0.3883131918452451</v>
       </c>
       <c r="C12">
-        <v>0.48730263068970492</v>
+        <v>0.4867107790756526</v>
       </c>
       <c r="D12">
-        <v>0.49810564010689817</v>
+        <v>0.4989293126925561</v>
       </c>
       <c r="E12">
-        <v>0.49655683494998509</v>
+        <v>0.4992538611304946</v>
       </c>
       <c r="F12">
-        <v>0.50965366978977944</v>
+        <v>0.511824027407431</v>
       </c>
       <c r="G12">
-        <v>0.4618597399612196</v>
+        <v>0.4655836917252834</v>
       </c>
       <c r="H12">
-        <v>0.44320941121710727</v>
+        <v>0.4449622707075437</v>
       </c>
       <c r="I12">
-        <v>0.41117030325964132</v>
+        <v>0.4130956328628702</v>
       </c>
       <c r="J12">
-        <v>0.38523214694076591</v>
+        <v>0.3840867305744434</v>
       </c>
       <c r="K12">
-        <v>0.37022072767356518</v>
+        <v>0.369568759493616</v>
       </c>
       <c r="L12">
-        <v>0.36154810007573462</v>
+        <v>0.3601832738930018</v>
       </c>
       <c r="M12">
-        <v>0.34956342511704319</v>
+        <v>0.3483873676263139</v>
       </c>
       <c r="N12">
-        <v>0.34868841989921151</v>
+        <v>0.3482641729895672</v>
       </c>
       <c r="O12">
-        <v>0.35353595521103659</v>
+        <v>0.3529206144446361</v>
       </c>
       <c r="P12">
-        <v>0.36077448259686518</v>
+        <v>0.3600807506861182</v>
       </c>
       <c r="Q12">
-        <v>0.37356972043958597</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>28</v>
+        <v>0.3719125848332266</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
+        </is>
       </c>
       <c r="B13">
-        <v>0.45595901834385549</v>
+        <v>0.4607882759562223</v>
       </c>
       <c r="C13">
-        <v>0.48787636984225319</v>
+        <v>0.4883000774622999</v>
       </c>
       <c r="D13">
-        <v>0.50850438955245081</v>
+        <v>0.5092289107394458</v>
       </c>
       <c r="E13">
-        <v>0.50751420317695151</v>
+        <v>0.5086789852588181</v>
       </c>
       <c r="F13">
-        <v>0.51229128334672325</v>
+        <v>0.5126827738803946</v>
       </c>
       <c r="G13">
-        <v>0.5203636914376718</v>
+        <v>0.5199881334011492</v>
       </c>
       <c r="H13">
-        <v>0.48630169462716649</v>
+        <v>0.4839479518496582</v>
       </c>
       <c r="I13">
-        <v>0.47928319336390568</v>
+        <v>0.4784562507663319</v>
       </c>
       <c r="J13">
-        <v>0.46352667932708003</v>
+        <v>0.4625220756543841</v>
       </c>
       <c r="K13">
-        <v>0.43932531523299378</v>
+        <v>0.4423429789255503</v>
       </c>
       <c r="L13">
-        <v>0.41908198550405001</v>
+        <v>0.4202856112290219</v>
       </c>
       <c r="M13">
-        <v>0.41501677921249019</v>
+        <v>0.4177377617199051</v>
       </c>
       <c r="N13">
-        <v>0.40959439485674509</v>
+        <v>0.4124419508884762</v>
       </c>
       <c r="O13">
-        <v>0.40622543004381889</v>
+        <v>0.4102437501285142</v>
       </c>
       <c r="P13">
-        <v>0.40292250014399028</v>
+        <v>0.4070102179237263</v>
       </c>
       <c r="Q13">
-        <v>0.40821222290124309</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>29</v>
+        <v>0.4124346261039041</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B14">
-        <v>0.39204598169801269</v>
+        <v>0.3953138287066144</v>
       </c>
       <c r="C14">
-        <v>0.4891184241482911</v>
+        <v>0.4893154505095809</v>
       </c>
       <c r="D14">
-        <v>0.49325821575880457</v>
+        <v>0.4931909105682126</v>
       </c>
       <c r="E14">
-        <v>0.51240994320443756</v>
+        <v>0.5126181506509825</v>
       </c>
       <c r="F14">
-        <v>0.51243562775136875</v>
+        <v>0.5142659169602585</v>
       </c>
       <c r="G14">
-        <v>0.52146318099498024</v>
+        <v>0.5258147799872229</v>
       </c>
       <c r="H14">
-        <v>0.51901188033507539</v>
+        <v>0.5221974572355668</v>
       </c>
       <c r="I14">
-        <v>0.48584636664523811</v>
+        <v>0.4883678250316236</v>
       </c>
       <c r="J14">
-        <v>0.45673389468212078</v>
+        <v>0.4599823936867001</v>
       </c>
       <c r="K14">
-        <v>0.45642905292756741</v>
+        <v>0.459491378407535</v>
       </c>
       <c r="L14">
-        <v>0.44536942887686642</v>
+        <v>0.4482598203843563</v>
       </c>
       <c r="M14">
-        <v>0.41755862499586072</v>
+        <v>0.4196545990415571</v>
       </c>
       <c r="N14">
-        <v>0.38364320052713469</v>
+        <v>0.3874817458458058</v>
       </c>
       <c r="O14">
-        <v>0.37246369707115151</v>
+        <v>0.3757797804421176</v>
       </c>
       <c r="P14">
-        <v>0.36149489058261158</v>
+        <v>0.3659828411378018</v>
       </c>
       <c r="Q14">
-        <v>0.35534341684885651</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>30</v>
+        <v>0.3587647198537247</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B15">
-        <v>0.40046196536068712</v>
+        <v>0.4004250533530196</v>
       </c>
       <c r="C15">
-        <v>0.48979288287810813</v>
+        <v>0.4902256665671618</v>
       </c>
       <c r="D15">
-        <v>0.49375375732629601</v>
+        <v>0.4943680519607214</v>
       </c>
       <c r="E15">
-        <v>0.51401476711387362</v>
+        <v>0.5138753660244602</v>
       </c>
       <c r="F15">
-        <v>0.51479390695501714</v>
+        <v>0.5148019205892108</v>
       </c>
       <c r="G15">
-        <v>0.52592096709023639</v>
+        <v>0.5264922364543307</v>
       </c>
       <c r="H15">
-        <v>0.52028890334335853</v>
+        <v>0.5250857473276089</v>
       </c>
       <c r="I15">
-        <v>0.48845332882581211</v>
+        <v>0.4903410052798544</v>
       </c>
       <c r="J15">
-        <v>0.46093277182415671</v>
+        <v>0.4622078185287672</v>
       </c>
       <c r="K15">
-        <v>0.46134343962635682</v>
+        <v>0.4650771721118666</v>
       </c>
       <c r="L15">
-        <v>0.44890040481639121</v>
+        <v>0.4502765355009604</v>
       </c>
       <c r="M15">
-        <v>0.42443802384613671</v>
+        <v>0.4226868651247893</v>
       </c>
       <c r="N15">
-        <v>0.39073142401128652</v>
+        <v>0.391316279284173</v>
       </c>
       <c r="O15">
-        <v>0.37725654741545112</v>
+        <v>0.3791216220194655</v>
       </c>
       <c r="P15">
-        <v>0.36687397913493991</v>
+        <v>0.3701925447916883</v>
       </c>
       <c r="Q15">
-        <v>0.36234419747346741</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>31</v>
+        <v>0.3624435010969766</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
+        </is>
       </c>
       <c r="B16">
-        <v>0.3963075859689319</v>
+        <v>0.3974855561162641</v>
       </c>
       <c r="C16">
-        <v>0.48888149685673132</v>
+        <v>0.4895097325757949</v>
       </c>
       <c r="D16">
-        <v>0.4929350934177773</v>
+        <v>0.4927301596249611</v>
       </c>
       <c r="E16">
-        <v>0.51370360339552379</v>
+        <v>0.5116941781750631</v>
       </c>
       <c r="F16">
-        <v>0.51481554823903808</v>
+        <v>0.5130986320139828</v>
       </c>
       <c r="G16">
-        <v>0.52607226540244889</v>
+        <v>0.5218424417430884</v>
       </c>
       <c r="H16">
-        <v>0.52368145631691743</v>
+        <v>0.5211519752193304</v>
       </c>
       <c r="I16">
-        <v>0.48959408993067111</v>
+        <v>0.4893204679386918</v>
       </c>
       <c r="J16">
-        <v>0.46275131261367958</v>
+        <v>0.4600577054194097</v>
       </c>
       <c r="K16">
-        <v>0.4619085005770357</v>
+        <v>0.4599235905623276</v>
       </c>
       <c r="L16">
-        <v>0.45011705327777152</v>
+        <v>0.4479405099106316</v>
       </c>
       <c r="M16">
-        <v>0.42408416366824792</v>
+        <v>0.4219075484090929</v>
       </c>
       <c r="N16">
-        <v>0.3903187544362533</v>
+        <v>0.388979612045709</v>
       </c>
       <c r="O16">
-        <v>0.37765763443903128</v>
+        <v>0.3746739632487901</v>
       </c>
       <c r="P16">
-        <v>0.36633518515343633</v>
+        <v>0.3638586758310591</v>
       </c>
       <c r="Q16">
-        <v>0.35808324613048498</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>32</v>
+        <v>0.3586979717624502</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B17">
-        <v>0.41178516657022579</v>
+        <v>0.4104045971310095</v>
       </c>
       <c r="C17">
-        <v>0.48866540120203289</v>
+        <v>0.4887401369146407</v>
       </c>
       <c r="D17">
-        <v>0.49266650069584828</v>
+        <v>0.4932807825168768</v>
       </c>
       <c r="E17">
-        <v>0.51287192822114636</v>
+        <v>0.5131764034897524</v>
       </c>
       <c r="F17">
-        <v>0.51476564256553059</v>
+        <v>0.5136305713708033</v>
       </c>
       <c r="G17">
-        <v>0.52418026596128819</v>
+        <v>0.5220307660940554</v>
       </c>
       <c r="H17">
-        <v>0.52181445593152975</v>
+        <v>0.5214394778748255</v>
       </c>
       <c r="I17">
-        <v>0.49029840133241642</v>
+        <v>0.4887038450315182</v>
       </c>
       <c r="J17">
-        <v>0.46443845397595562</v>
+        <v>0.4623312731664756</v>
       </c>
       <c r="K17">
-        <v>0.46664674921010141</v>
+        <v>0.4639056355618676</v>
       </c>
       <c r="L17">
-        <v>0.45594867045233167</v>
+        <v>0.4526378575590124</v>
       </c>
       <c r="M17">
-        <v>0.43228103317591082</v>
+        <v>0.4300745274180369</v>
       </c>
       <c r="N17">
-        <v>0.40076125487056963</v>
+        <v>0.3996845179616462</v>
       </c>
       <c r="O17">
-        <v>0.38675693701605912</v>
+        <v>0.3878385367907338</v>
       </c>
       <c r="P17">
-        <v>0.37371331095095922</v>
+        <v>0.375702788929017</v>
       </c>
       <c r="Q17">
-        <v>0.36583213715699209</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>33</v>
+        <v>0.3681530381585914</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B18">
-        <v>0.38840810871315079</v>
+        <v>0.3855395356175562</v>
       </c>
       <c r="C18">
-        <v>0.48723431769412279</v>
+        <v>0.486862566695043</v>
       </c>
       <c r="D18">
-        <v>0.49887178436064572</v>
+        <v>0.4994378150464132</v>
       </c>
       <c r="E18">
-        <v>0.49809960041234502</v>
+        <v>0.5004614798636534</v>
       </c>
       <c r="F18">
-        <v>0.51347273204366362</v>
+        <v>0.5136852789073979</v>
       </c>
       <c r="G18">
-        <v>0.46263763815289571</v>
+        <v>0.460299735609072</v>
       </c>
       <c r="H18">
-        <v>0.4322998868506609</v>
+        <v>0.4318494509050322</v>
       </c>
       <c r="I18">
-        <v>0.41633364299596681</v>
+        <v>0.4152367618698413</v>
       </c>
       <c r="J18">
-        <v>0.38782029122312672</v>
+        <v>0.3875024413356137</v>
       </c>
       <c r="K18">
-        <v>0.3698447688254814</v>
+        <v>0.3700852602912252</v>
       </c>
       <c r="L18">
-        <v>0.36262670682729781</v>
+        <v>0.364148721475167</v>
       </c>
       <c r="M18">
-        <v>0.35329048413745823</v>
+        <v>0.3541439330214875</v>
       </c>
       <c r="N18">
-        <v>0.35219140314230052</v>
+        <v>0.3520917805201244</v>
       </c>
       <c r="O18">
-        <v>0.36061003570559991</v>
+        <v>0.3607426982082129</v>
       </c>
       <c r="P18">
-        <v>0.36823029165996729</v>
+        <v>0.3687616051926433</v>
       </c>
       <c r="Q18">
-        <v>0.37220849531604222</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>34</v>
+        <v>0.3740881784816181</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B19">
-        <v>0.37952834717904438</v>
+        <v>0.3813235128307108</v>
       </c>
       <c r="C19">
-        <v>0.48768239368197192</v>
+        <v>0.4873828742199461</v>
       </c>
       <c r="D19">
-        <v>0.50141526543637227</v>
+        <v>0.5005927367964744</v>
       </c>
       <c r="E19">
-        <v>0.50340340541303141</v>
+        <v>0.5022179494868179</v>
       </c>
       <c r="F19">
-        <v>0.50053808127863864</v>
+        <v>0.5036944808147601</v>
       </c>
       <c r="G19">
-        <v>0.44640344843831908</v>
+        <v>0.4455717058626081</v>
       </c>
       <c r="H19">
-        <v>0.40972855341419462</v>
+        <v>0.4120866135415515</v>
       </c>
       <c r="I19">
-        <v>0.39602569540157012</v>
+        <v>0.3970714525506798</v>
       </c>
       <c r="J19">
-        <v>0.37281505586235331</v>
+        <v>0.374106803170845</v>
       </c>
       <c r="K19">
-        <v>0.35724178610489288</v>
+        <v>0.3594717395693051</v>
       </c>
       <c r="L19">
-        <v>0.3509597278889468</v>
+        <v>0.3528132882401501</v>
       </c>
       <c r="M19">
-        <v>0.34592057324882119</v>
+        <v>0.3462041634601196</v>
       </c>
       <c r="N19">
-        <v>0.34498343498931971</v>
+        <v>0.3446072759757995</v>
       </c>
       <c r="O19">
-        <v>0.34771242019564008</v>
+        <v>0.3465545984726394</v>
       </c>
       <c r="P19">
-        <v>0.34467041522569641</v>
+        <v>0.3450722449462176</v>
       </c>
       <c r="Q19">
-        <v>0.34530608722366579</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>35</v>
+        <v>0.34709552495685</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B20">
-        <v>0.37567258961250949</v>
+        <v>0.380531065350338</v>
       </c>
       <c r="C20">
-        <v>0.48742494459393199</v>
+        <v>0.4870985003238467</v>
       </c>
       <c r="D20">
-        <v>0.49545294247930283</v>
+        <v>0.4939381314586508</v>
       </c>
       <c r="E20">
-        <v>0.50148419756094531</v>
+        <v>0.502408306709099</v>
       </c>
       <c r="F20">
-        <v>0.47837083315229162</v>
+        <v>0.479434785548053</v>
       </c>
       <c r="G20">
-        <v>0.43543340804534048</v>
+        <v>0.4387284146836714</v>
       </c>
       <c r="H20">
-        <v>0.42619761496716368</v>
+        <v>0.4309825990796646</v>
       </c>
       <c r="I20">
-        <v>0.39892744450374468</v>
+        <v>0.4031908148467622</v>
       </c>
       <c r="J20">
-        <v>0.37857706657870882</v>
+        <v>0.3808312038751483</v>
       </c>
       <c r="K20">
-        <v>0.36730301443525121</v>
+        <v>0.3689990874367589</v>
       </c>
       <c r="L20">
-        <v>0.35147916607550961</v>
+        <v>0.3541756965734822</v>
       </c>
       <c r="M20">
-        <v>0.34529409839272079</v>
+        <v>0.3479443586735576</v>
       </c>
       <c r="N20">
-        <v>0.35042249550378279</v>
-      </c>
-      <c r="O20" s="2">
-        <v>0.33372001351245528</v>
+        <v>0.3522800974534042</v>
+      </c>
+      <c r="O20">
+        <v>0.3354307254366742</v>
       </c>
       <c r="P20">
-        <v>0.33505022070399632</v>
+        <v>0.3370395213298006</v>
       </c>
       <c r="Q20">
-        <v>0.33598664522133942</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>36</v>
+        <v>0.3399389942229843</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B21">
-        <v>0.43648127433916262</v>
+        <v>0.4419606725372274</v>
       </c>
       <c r="C21">
-        <v>0.48668392784257508</v>
+        <v>0.4863522624717752</v>
       </c>
       <c r="D21">
-        <v>0.49027132518001648</v>
+        <v>0.4905307788718875</v>
       </c>
       <c r="E21">
-        <v>0.51363296854781382</v>
+        <v>0.5167241929307235</v>
       </c>
       <c r="F21">
-        <v>0.47370584893489848</v>
+        <v>0.4784047765299551</v>
       </c>
       <c r="G21">
-        <v>0.45658853257884641</v>
+        <v>0.4589981984494294</v>
       </c>
       <c r="H21">
-        <v>0.44823546323915481</v>
+        <v>0.4498026655708093</v>
       </c>
       <c r="I21">
-        <v>0.4373573268037787</v>
+        <v>0.4380996006106974</v>
       </c>
       <c r="J21">
-        <v>0.42217341540848469</v>
+        <v>0.4273998237971877</v>
       </c>
       <c r="K21">
-        <v>0.40324353544236119</v>
+        <v>0.403722185703134</v>
       </c>
       <c r="L21">
-        <v>0.3909494779640052</v>
+        <v>0.3922910829762944</v>
       </c>
       <c r="M21">
-        <v>0.38448521216806231</v>
+        <v>0.3856632836119026</v>
       </c>
       <c r="N21">
-        <v>0.38855012648184722</v>
+        <v>0.3885977328076934</v>
       </c>
       <c r="O21">
-        <v>0.39733135319216839</v>
+        <v>0.395777892472686</v>
       </c>
       <c r="P21">
-        <v>0.40026947570153998</v>
+        <v>0.3989880345931693</v>
       </c>
       <c r="Q21">
-        <v>0.39745645911755939</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>37</v>
+        <v>0.3954382313900986</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B22">
-        <v>0.44867101666961268</v>
+        <v>0.4500141918034271</v>
       </c>
       <c r="C22">
-        <v>0.48572431858169662</v>
+        <v>0.4866183042694504</v>
       </c>
       <c r="D22">
-        <v>0.49010736899987822</v>
+        <v>0.4910216876149196</v>
       </c>
       <c r="E22">
-        <v>0.51286842910263086</v>
+        <v>0.5153257585212354</v>
       </c>
       <c r="F22">
-        <v>0.47265729607895579</v>
+        <v>0.4740853291069787</v>
       </c>
       <c r="G22">
-        <v>0.45451243617144482</v>
+        <v>0.4571411177737191</v>
       </c>
       <c r="H22">
-        <v>0.44975908728060532</v>
+        <v>0.4508773726581265</v>
       </c>
       <c r="I22">
-        <v>0.44270476409451448</v>
+        <v>0.4438702789084905</v>
       </c>
       <c r="J22">
-        <v>0.43450946258432088</v>
+        <v>0.4378541019943484</v>
       </c>
       <c r="K22">
-        <v>0.41176598235180062</v>
+        <v>0.4146713958577131</v>
       </c>
       <c r="L22">
-        <v>0.40014802069243288</v>
+        <v>0.4048542131521896</v>
       </c>
       <c r="M22">
-        <v>0.3952833595422891</v>
+        <v>0.4007235317243151</v>
       </c>
       <c r="N22">
-        <v>0.39471082844579358</v>
+        <v>0.3997205981117217</v>
       </c>
       <c r="O22">
-        <v>0.39703090086895332</v>
+        <v>0.402216684342632</v>
       </c>
       <c r="P22">
-        <v>0.39734416405366241</v>
+        <v>0.4030773149551162</v>
       </c>
       <c r="Q22">
-        <v>0.39784908467576402</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>38</v>
+        <v>0.4042788299557485</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B23">
-        <v>0.38555606639507428</v>
+        <v>0.3853845899843697</v>
       </c>
       <c r="C23">
-        <v>0.48683692720411131</v>
+        <v>0.4860050112624487</v>
       </c>
       <c r="D23">
-        <v>0.50196032066267837</v>
+        <v>0.5020195437896152</v>
       </c>
       <c r="E23">
-        <v>0.46989869577234389</v>
+        <v>0.4656859507712289</v>
       </c>
       <c r="F23">
-        <v>0.45400760936195222</v>
+        <v>0.4522066390948386</v>
       </c>
       <c r="G23">
-        <v>0.40768683852028442</v>
+        <v>0.4058224783526301</v>
       </c>
       <c r="H23">
-        <v>0.38167794701759361</v>
+        <v>0.3795732597233188</v>
       </c>
       <c r="I23">
-        <v>0.36922401091743479</v>
+        <v>0.3674776685820385</v>
       </c>
       <c r="J23">
-        <v>0.35974731162588192</v>
+        <v>0.3575663147918921</v>
       </c>
       <c r="K23">
-        <v>0.35041021364763342</v>
+        <v>0.3495100905140385</v>
       </c>
       <c r="L23">
-        <v>0.34768650853566258</v>
+        <v>0.3489334340566729</v>
       </c>
       <c r="M23">
-        <v>0.34761094342430598</v>
+        <v>0.3499039166544538</v>
       </c>
       <c r="N23">
-        <v>0.35573320806786007</v>
+        <v>0.35802272891149</v>
       </c>
       <c r="O23">
-        <v>0.35967032053573139</v>
+        <v>0.3616511145743414</v>
       </c>
       <c r="P23">
-        <v>0.36352934117814528</v>
+        <v>0.3666934078192942</v>
       </c>
       <c r="Q23">
-        <v>0.37306507966926589</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>39</v>
+        <v>0.375016238805594</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B24">
-        <v>0.49724652293631338</v>
+        <v>0.4978423131182571</v>
       </c>
       <c r="C24">
-        <v>0.49712843549385971</v>
+        <v>0.4978423131182571</v>
       </c>
       <c r="D24">
-        <v>0.48196380061671518</v>
+        <v>0.4824603984462625</v>
       </c>
       <c r="E24">
-        <v>0.47523570896760342</v>
+        <v>0.47762938126534</v>
       </c>
       <c r="F24">
-        <v>0.47883828294013292</v>
+        <v>0.4809584101053277</v>
       </c>
       <c r="G24">
-        <v>0.49116630723136878</v>
+        <v>0.4928166413780476</v>
       </c>
       <c r="H24">
-        <v>0.50673769942382529</v>
+        <v>0.5098086648174373</v>
       </c>
       <c r="I24">
-        <v>0.50223819220599453</v>
+        <v>0.5047640140015078</v>
       </c>
       <c r="J24">
-        <v>0.50398741087320376</v>
+        <v>0.5071160354003956</v>
       </c>
       <c r="K24">
-        <v>0.52306417608314193</v>
+        <v>0.524943542378501</v>
       </c>
       <c r="L24">
-        <v>0.55288103607756545</v>
+        <v>0.5555453688507769</v>
       </c>
       <c r="M24">
-        <v>0.55398453124510016</v>
+        <v>0.558348693592926</v>
       </c>
       <c r="N24">
-        <v>0.5608924608357666</v>
+        <v>0.5651959333115628</v>
       </c>
       <c r="O24">
-        <v>0.57144911030458401</v>
+        <v>0.5781902276298897</v>
       </c>
       <c r="P24">
-        <v>0.58736265614832506</v>
+        <v>0.5910817280890365</v>
       </c>
       <c r="Q24">
-        <v>0.60472342800042456</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>40</v>
+        <v>0.6065679619946295</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B25">
-        <v>0.54132414447633281</v>
+        <v>0.5400061297263863</v>
       </c>
       <c r="C25">
-        <v>0.5413241444763327</v>
+        <v>0.5400061297263863</v>
       </c>
       <c r="D25">
-        <v>0.51952536024498253</v>
+        <v>0.5176974169693979</v>
       </c>
       <c r="E25">
-        <v>0.50787351057060026</v>
+        <v>0.5066207708380001</v>
       </c>
       <c r="F25">
-        <v>0.50263941988976024</v>
+        <v>0.502232533088848</v>
       </c>
       <c r="G25">
-        <v>0.52711343623344298</v>
+        <v>0.5250453793664729</v>
       </c>
       <c r="H25">
-        <v>0.53796482072164054</v>
+        <v>0.5355596586858083</v>
       </c>
       <c r="I25">
-        <v>0.5390490352045878</v>
+        <v>0.5364424833389061</v>
       </c>
       <c r="J25">
-        <v>0.53045175661662591</v>
+        <v>0.5285316544662825</v>
       </c>
       <c r="K25">
-        <v>0.53241216976123706</v>
+        <v>0.5322059426600322</v>
       </c>
       <c r="L25">
-        <v>0.54906478843085393</v>
+        <v>0.5507607676111118</v>
       </c>
       <c r="M25">
-        <v>0.55661380192624066</v>
+        <v>0.5592124607173055</v>
       </c>
       <c r="N25">
-        <v>0.57841555738093842</v>
+        <v>0.581020006206845</v>
       </c>
       <c r="O25">
-        <v>0.59609832972026933</v>
+        <v>0.6001231398948311</v>
       </c>
       <c r="P25">
-        <v>0.60564680215698219</v>
+        <v>0.6095664191868998</v>
       </c>
       <c r="Q25">
-        <v>0.61257521769775092</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>41</v>
+        <v>0.6132506031004228</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B26">
-        <v>0.50017257312703178</v>
+        <v>0.4988176487927437</v>
       </c>
       <c r="C26">
-        <v>0.50170247842659599</v>
+        <v>0.5012032770186075</v>
       </c>
       <c r="D26">
-        <v>0.48072857208475128</v>
+        <v>0.4798429185558821</v>
       </c>
       <c r="E26">
-        <v>0.47106934134517592</v>
+        <v>0.4717046016484175</v>
       </c>
       <c r="F26">
-        <v>0.46397882401446688</v>
+        <v>0.4642294226422148</v>
       </c>
       <c r="G26">
-        <v>0.46485732811163799</v>
+        <v>0.4653853967702961</v>
       </c>
       <c r="H26">
-        <v>0.45397076587774732</v>
+        <v>0.4556391795455395</v>
       </c>
       <c r="I26">
-        <v>0.45152812096582062</v>
+        <v>0.4528729688877901</v>
       </c>
       <c r="J26">
-        <v>0.45365861375289818</v>
+        <v>0.4538230290466383</v>
       </c>
       <c r="K26">
-        <v>0.44933225767792262</v>
+        <v>0.4495364792549903</v>
       </c>
       <c r="L26">
-        <v>0.44889597367216177</v>
+        <v>0.4469300419726782</v>
       </c>
       <c r="M26">
-        <v>0.45651667667172369</v>
+        <v>0.4542092334680851</v>
       </c>
       <c r="N26">
-        <v>0.4592580929540902</v>
+        <v>0.4584415089810182</v>
       </c>
       <c r="O26">
-        <v>0.46766756037005502</v>
+        <v>0.4665938574139014</v>
       </c>
       <c r="P26">
-        <v>0.4771367874002358</v>
+        <v>0.4748434404863817</v>
       </c>
       <c r="Q26">
-        <v>0.48597780986833428</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>42</v>
+        <v>0.4842263791264303</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B27">
-        <v>0.50494413499383828</v>
+        <v>0.5050873180733021</v>
       </c>
       <c r="C27">
-        <v>0.50534795224601248</v>
+        <v>0.5058264414601903</v>
       </c>
       <c r="D27">
-        <v>0.4876040862207115</v>
+        <v>0.4873592267006607</v>
       </c>
       <c r="E27">
-        <v>0.46568059215509972</v>
+        <v>0.46351901511337</v>
       </c>
       <c r="F27">
-        <v>0.45573870630471031</v>
+        <v>0.4578405072043461</v>
       </c>
       <c r="G27">
-        <v>0.46544259248120951</v>
+        <v>0.4658069951709828</v>
       </c>
       <c r="H27">
-        <v>0.46573758955139538</v>
+        <v>0.4662308631257122</v>
       </c>
       <c r="I27">
-        <v>0.47045522135930318</v>
+        <v>0.471158126002531</v>
       </c>
       <c r="J27">
-        <v>0.48941723711098839</v>
+        <v>0.4885591163703186</v>
       </c>
       <c r="K27">
-        <v>0.48405960188830183</v>
+        <v>0.4848687682911873</v>
       </c>
       <c r="L27">
-        <v>0.4814133709608443</v>
+        <v>0.4825092851938545</v>
       </c>
       <c r="M27">
-        <v>0.47370139592773192</v>
+        <v>0.4755360454325566</v>
       </c>
       <c r="N27">
-        <v>0.4693542032887088</v>
+        <v>0.4715224026794091</v>
       </c>
       <c r="O27">
-        <v>0.47098241395287288</v>
+        <v>0.4722925365233541</v>
       </c>
       <c r="P27">
-        <v>0.4857964353278692</v>
+        <v>0.4879046201749622</v>
       </c>
       <c r="Q27">
-        <v>0.49765074820512212</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>43</v>
+        <v>0.4990261585207267</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B28">
-        <v>0.46164683802841761</v>
+        <v>0.4611816079144779</v>
       </c>
       <c r="C28">
-        <v>0.49029702839252431</v>
+        <v>0.4901545718026233</v>
       </c>
       <c r="D28">
-        <v>0.51390297457446554</v>
+        <v>0.5135545097871825</v>
       </c>
       <c r="E28">
-        <v>0.51704739096251517</v>
+        <v>0.5176362121906282</v>
       </c>
       <c r="F28">
-        <v>0.51059490749348613</v>
+        <v>0.5112205582268371</v>
       </c>
       <c r="G28">
-        <v>0.5109914851999029</v>
+        <v>0.5120750710295662</v>
       </c>
       <c r="H28">
-        <v>0.49457059249153701</v>
+        <v>0.4946521869599911</v>
       </c>
       <c r="I28">
-        <v>0.51348849249792916</v>
+        <v>0.5103948231306611</v>
       </c>
       <c r="J28">
-        <v>0.49048588602975629</v>
+        <v>0.4904331394058839</v>
       </c>
       <c r="K28">
-        <v>0.44723052955707632</v>
+        <v>0.4490031185425392</v>
       </c>
       <c r="L28">
-        <v>0.42701385598126462</v>
+        <v>0.4245446840308332</v>
       </c>
       <c r="M28">
-        <v>0.41399998554321488</v>
+        <v>0.4136891080601499</v>
       </c>
       <c r="N28">
-        <v>0.41899522155668201</v>
+        <v>0.4200336777160126</v>
       </c>
       <c r="O28">
-        <v>0.43679649266441628</v>
+        <v>0.438422053349179</v>
       </c>
       <c r="P28">
-        <v>0.45000211363239728</v>
+        <v>0.4509458610196682</v>
       </c>
       <c r="Q28">
-        <v>0.46843320185690063</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>44</v>
+        <v>0.470487522756556</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B29">
-        <v>0.46412385471649542</v>
+        <v>0.4623183628632481</v>
       </c>
       <c r="C29">
-        <v>0.49122024562847549</v>
+        <v>0.4910377906085563</v>
       </c>
       <c r="D29">
-        <v>0.51602537140746352</v>
+        <v>0.5155751683778349</v>
       </c>
       <c r="E29">
-        <v>0.51785048160626745</v>
+        <v>0.5174630230071732</v>
       </c>
       <c r="F29">
-        <v>0.50964887343320198</v>
+        <v>0.5089317776725171</v>
       </c>
       <c r="G29">
-        <v>0.50714607353715735</v>
+        <v>0.5074063609379756</v>
       </c>
       <c r="H29">
-        <v>0.50213613715787708</v>
+        <v>0.5027229321797058</v>
       </c>
       <c r="I29">
-        <v>0.51981459869708235</v>
+        <v>0.5197917636414702</v>
       </c>
       <c r="J29">
-        <v>0.50917459770544171</v>
+        <v>0.5041124239373004</v>
       </c>
       <c r="K29">
-        <v>0.48553200405273922</v>
+        <v>0.48561192477438</v>
       </c>
       <c r="L29">
-        <v>0.43333529705517548</v>
+        <v>0.4337143189706792</v>
       </c>
       <c r="M29">
-        <v>0.42354866913811468</v>
+        <v>0.4246344032075633</v>
       </c>
       <c r="N29">
-        <v>0.41716952555121412</v>
+        <v>0.4165586214431846</v>
       </c>
       <c r="O29">
-        <v>0.42547524195569481</v>
+        <v>0.4256422654163916</v>
       </c>
       <c r="P29">
-        <v>0.44043874664436378</v>
+        <v>0.4390886562362231</v>
       </c>
       <c r="Q29">
-        <v>0.45470091184674011</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>45</v>
+        <v>0.454468899977561</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B30">
-        <v>0.47459450778912737</v>
+        <v>0.4799749547767684</v>
       </c>
       <c r="C30">
-        <v>0.49055806277035729</v>
+        <v>0.4900729021036209</v>
       </c>
       <c r="D30">
-        <v>0.51686936645731174</v>
+        <v>0.5158256868850122</v>
       </c>
       <c r="E30">
-        <v>0.51225701292755355</v>
+        <v>0.5107391349332195</v>
       </c>
       <c r="F30">
-        <v>0.5029575388302876</v>
+        <v>0.5009925746156486</v>
       </c>
       <c r="G30">
-        <v>0.51030527739719178</v>
+        <v>0.5113830696088834</v>
       </c>
       <c r="H30">
-        <v>0.50319792796512242</v>
+        <v>0.5043360760127674</v>
       </c>
       <c r="I30">
-        <v>0.47263999273856577</v>
+        <v>0.4747242410588582</v>
       </c>
       <c r="J30">
-        <v>0.4859307159113449</v>
+        <v>0.4879629232024878</v>
       </c>
       <c r="K30">
-        <v>0.44826669021524668</v>
+        <v>0.4511334270840363</v>
       </c>
       <c r="L30">
-        <v>0.42583398792223198</v>
+        <v>0.4271685254268249</v>
       </c>
       <c r="M30">
-        <v>0.42748442429957162</v>
+        <v>0.4264703281042194</v>
       </c>
       <c r="N30">
-        <v>0.43336077337357642</v>
+        <v>0.4310901528120369</v>
       </c>
       <c r="O30">
-        <v>0.44453348759123612</v>
+        <v>0.4412636729011281</v>
       </c>
       <c r="P30">
-        <v>0.45714234098066048</v>
+        <v>0.455422284256189</v>
       </c>
       <c r="Q30">
-        <v>0.47446892003013569</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>46</v>
+        <v>0.4739368179348245</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B31">
-        <v>0.43263435509060211</v>
+        <v>0.4281597031812618</v>
       </c>
       <c r="C31">
-        <v>0.48967996674648678</v>
+        <v>0.490940410980074</v>
       </c>
       <c r="D31">
-        <v>0.51586727615197348</v>
+        <v>0.5166683569286185</v>
       </c>
       <c r="E31">
-        <v>0.51172663517448269</v>
+        <v>0.5126193335921969</v>
       </c>
       <c r="F31">
-        <v>0.50064124438444002</v>
+        <v>0.5017736037805177</v>
       </c>
       <c r="G31">
-        <v>0.50902544495035462</v>
+        <v>0.5092970317446319</v>
       </c>
       <c r="H31">
-        <v>0.50257945318561614</v>
+        <v>0.5036323438783086</v>
       </c>
       <c r="I31">
-        <v>0.47614588124930518</v>
+        <v>0.4772822218018951</v>
       </c>
       <c r="J31">
-        <v>0.48692336637306027</v>
+        <v>0.4904221795594829</v>
       </c>
       <c r="K31">
-        <v>0.45520030310428372</v>
+        <v>0.4565045410959014</v>
       </c>
       <c r="L31">
-        <v>0.41735436175890822</v>
+        <v>0.4165571732455413</v>
       </c>
       <c r="M31">
-        <v>0.40710220233938338</v>
+        <v>0.4054870709790321</v>
       </c>
       <c r="N31">
-        <v>0.40301133297097369</v>
+        <v>0.4019139092367707</v>
       </c>
       <c r="O31">
-        <v>0.40295888363194859</v>
+        <v>0.4012109205952086</v>
       </c>
       <c r="P31">
-        <v>0.4101849020174394</v>
+        <v>0.4061890217436868</v>
       </c>
       <c r="Q31">
-        <v>0.41325562255501552</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>47</v>
+        <v>0.4088509540963157</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B32">
-        <v>0.44156376187185431</v>
+        <v>0.4386225962208765</v>
       </c>
       <c r="C32">
-        <v>0.49062617613816062</v>
+        <v>0.4903679302322791</v>
       </c>
       <c r="D32">
-        <v>0.51535124577178626</v>
+        <v>0.5144223501563832</v>
       </c>
       <c r="E32">
-        <v>0.5179387783499555</v>
+        <v>0.5171300727583678</v>
       </c>
       <c r="F32">
-        <v>0.51022163733756154</v>
+        <v>0.5089325954341146</v>
       </c>
       <c r="G32">
-        <v>0.50820978519075877</v>
+        <v>0.5068902984097564</v>
       </c>
       <c r="H32">
-        <v>0.50390122939889936</v>
+        <v>0.50283532315473</v>
       </c>
       <c r="I32">
-        <v>0.51715579300346393</v>
+        <v>0.5146607500882697</v>
       </c>
       <c r="J32">
-        <v>0.51029497214719444</v>
+        <v>0.5100030695525903</v>
       </c>
       <c r="K32">
-        <v>0.49128289757964538</v>
+        <v>0.4923000354501648</v>
       </c>
       <c r="L32">
-        <v>0.43325745115742009</v>
+        <v>0.43306770434676</v>
       </c>
       <c r="M32">
-        <v>0.41531330658803978</v>
+        <v>0.4143212570014371</v>
       </c>
       <c r="N32">
-        <v>0.41162987839794052</v>
+        <v>0.4101906717650063</v>
       </c>
       <c r="O32">
-        <v>0.41100650532523347</v>
+        <v>0.4075920741776709</v>
       </c>
       <c r="P32">
-        <v>0.41552964143614662</v>
+        <v>0.4141591631954395</v>
       </c>
       <c r="Q32">
-        <v>0.41658109728485843</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>48</v>
+        <v>0.4133968277919634</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B33">
-        <v>0.42850434659090803</v>
+        <v>0.4289303576738948</v>
       </c>
       <c r="C33">
-        <v>0.49148732953823898</v>
+        <v>0.4906279677614293</v>
       </c>
       <c r="D33">
-        <v>0.51598494252587668</v>
+        <v>0.5153321831238024</v>
       </c>
       <c r="E33">
-        <v>0.51833372538746125</v>
+        <v>0.5174477663450945</v>
       </c>
       <c r="F33">
-        <v>0.50959109135720437</v>
+        <v>0.5092104693496751</v>
       </c>
       <c r="G33">
-        <v>0.50728803081783513</v>
+        <v>0.5070246970796417</v>
       </c>
       <c r="H33">
-        <v>0.50291059951457662</v>
+        <v>0.5022071521565608</v>
       </c>
       <c r="I33">
-        <v>0.51730862334255301</v>
+        <v>0.514462699151768</v>
       </c>
       <c r="J33">
-        <v>0.50793974716963119</v>
+        <v>0.5079301845417151</v>
       </c>
       <c r="K33">
-        <v>0.49052410425064569</v>
+        <v>0.4912331540287647</v>
       </c>
       <c r="L33">
-        <v>0.42817236268934827</v>
+        <v>0.4261787508164412</v>
       </c>
       <c r="M33">
-        <v>0.41144750479415221</v>
+        <v>0.4114664937092318</v>
       </c>
       <c r="N33">
-        <v>0.40509342791669739</v>
+        <v>0.4063184102532829</v>
       </c>
       <c r="O33">
-        <v>0.40300040101655338</v>
+        <v>0.4031661219816582</v>
       </c>
       <c r="P33">
-        <v>0.40652268768377481</v>
+        <v>0.4049629353993432</v>
       </c>
       <c r="Q33">
-        <v>0.40470841840513477</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>49</v>
+        <v>0.4034411271217889</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
+        </is>
       </c>
       <c r="B34">
-        <v>0.42785895493487908</v>
+        <v>0.4320080261363073</v>
       </c>
       <c r="C34">
-        <v>0.49050996865846369</v>
+        <v>0.4907224744673418</v>
       </c>
       <c r="D34">
-        <v>0.51531423268292709</v>
+        <v>0.5146483589432647</v>
       </c>
       <c r="E34">
-        <v>0.51749068504414053</v>
+        <v>0.5172244717361116</v>
       </c>
       <c r="F34">
-        <v>0.5098630822714969</v>
+        <v>0.5093589354243597</v>
       </c>
       <c r="G34">
-        <v>0.50841366677114386</v>
+        <v>0.5066089382450901</v>
       </c>
       <c r="H34">
-        <v>0.50357541703491948</v>
+        <v>0.5008891158522651</v>
       </c>
       <c r="I34">
-        <v>0.51524545204053918</v>
+        <v>0.5135355582791706</v>
       </c>
       <c r="J34">
-        <v>0.51066544092030008</v>
+        <v>0.510429131962103</v>
       </c>
       <c r="K34">
-        <v>0.49378730953853822</v>
+        <v>0.4933892852729858</v>
       </c>
       <c r="L34">
-        <v>0.42981997671678163</v>
+        <v>0.4287582224878047</v>
       </c>
       <c r="M34">
-        <v>0.41695404234585409</v>
+        <v>0.4149714511311657</v>
       </c>
       <c r="N34">
-        <v>0.40898651778307188</v>
+        <v>0.4092066966387115</v>
       </c>
       <c r="O34">
-        <v>0.40728478904696452</v>
+        <v>0.4092726505778744</v>
       </c>
       <c r="P34">
-        <v>0.41191292195832002</v>
+        <v>0.4080952127370809</v>
       </c>
       <c r="Q34">
-        <v>0.40899666770534782</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>50</v>
+        <v>0.4086659536083933</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
+        </is>
       </c>
       <c r="B35">
-        <v>0.43274322785459568</v>
+        <v>0.4344004126913853</v>
       </c>
       <c r="C35">
-        <v>0.4923082591776578</v>
+        <v>0.4912016115656417</v>
       </c>
       <c r="D35">
-        <v>0.51610269074524917</v>
+        <v>0.5155795028610738</v>
       </c>
       <c r="E35">
-        <v>0.51930452010691097</v>
+        <v>0.5192002975394762</v>
       </c>
       <c r="F35">
-        <v>0.51194578108019151</v>
+        <v>0.5105924520528484</v>
       </c>
       <c r="G35">
-        <v>0.5105090949242912</v>
+        <v>0.5087207029467283</v>
       </c>
       <c r="H35">
-        <v>0.50474575439966041</v>
+        <v>0.5039908485223258</v>
       </c>
       <c r="I35">
-        <v>0.51658803850911128</v>
+        <v>0.5183371566615581</v>
       </c>
       <c r="J35">
-        <v>0.51305262865870371</v>
+        <v>0.5152410363441087</v>
       </c>
       <c r="K35">
-        <v>0.49890929835222958</v>
+        <v>0.499955713131003</v>
       </c>
       <c r="L35">
-        <v>0.43535777701088418</v>
+        <v>0.4364305711611154</v>
       </c>
       <c r="M35">
-        <v>0.42017468120809681</v>
+        <v>0.4211747536869107</v>
       </c>
       <c r="N35">
-        <v>0.41289708202957381</v>
+        <v>0.4127215614966557</v>
       </c>
       <c r="O35">
-        <v>0.40775076258483461</v>
+        <v>0.4074829120761207</v>
       </c>
       <c r="P35">
-        <v>0.40886488972221718</v>
+        <v>0.4087599644733571</v>
       </c>
       <c r="Q35">
-        <v>0.403231132715902</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>51</v>
+        <v>0.4032297040340295</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B36">
-        <v>0.44261301008207898</v>
+        <v>0.4488870253588377</v>
       </c>
       <c r="C36">
-        <v>0.49089064546703648</v>
+        <v>0.4913115845919304</v>
       </c>
       <c r="D36">
-        <v>0.514497637477773</v>
+        <v>0.5164034999485476</v>
       </c>
       <c r="E36">
-        <v>0.51724215160104781</v>
+        <v>0.5188361490498071</v>
       </c>
       <c r="F36">
-        <v>0.50877914485310438</v>
+        <v>0.5101714312750559</v>
       </c>
       <c r="G36">
-        <v>0.50691980636116307</v>
+        <v>0.5090801840664879</v>
       </c>
       <c r="H36">
-        <v>0.50259809904027553</v>
+        <v>0.5044527602479003</v>
       </c>
       <c r="I36">
-        <v>0.51642942378611012</v>
+        <v>0.5171240850922505</v>
       </c>
       <c r="J36">
-        <v>0.50760615460710623</v>
+        <v>0.5105011734780546</v>
       </c>
       <c r="K36">
-        <v>0.48928634571373181</v>
+        <v>0.4930561364908898</v>
       </c>
       <c r="L36">
-        <v>0.43034544732763502</v>
+        <v>0.4330517845329634</v>
       </c>
       <c r="M36">
-        <v>0.41556026650787259</v>
+        <v>0.4152528996671885</v>
       </c>
       <c r="N36">
-        <v>0.41078806053928169</v>
+        <v>0.4078634525652465</v>
       </c>
       <c r="O36">
-        <v>0.41214004778574131</v>
+        <v>0.4111315971122282</v>
       </c>
       <c r="P36">
-        <v>0.42080680078353649</v>
+        <v>0.4195655964146631</v>
       </c>
       <c r="Q36">
-        <v>0.42464812479314129</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>52</v>
+        <v>0.4239378973405217</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
+        </is>
       </c>
       <c r="B37">
-        <v>0.43924650538697002</v>
+        <v>0.4396520607456376</v>
       </c>
       <c r="C37">
-        <v>0.48997433929061751</v>
+        <v>0.4907839492586203</v>
       </c>
       <c r="D37">
-        <v>0.51408367497592022</v>
+        <v>0.5134493723240851</v>
       </c>
       <c r="E37">
-        <v>0.51679869978893656</v>
+        <v>0.5156923963200787</v>
       </c>
       <c r="F37">
-        <v>0.50956051210522291</v>
+        <v>0.5078151908424405</v>
       </c>
       <c r="G37">
-        <v>0.50743652057506439</v>
+        <v>0.5061404839936999</v>
       </c>
       <c r="H37">
-        <v>0.50204845254974151</v>
+        <v>0.500462331135655</v>
       </c>
       <c r="I37">
-        <v>0.51765835289371631</v>
+        <v>0.5140687016523952</v>
       </c>
       <c r="J37">
-        <v>0.51095043581784638</v>
+        <v>0.5078122188277238</v>
       </c>
       <c r="K37">
-        <v>0.49410050905091207</v>
+        <v>0.4906938124039997</v>
       </c>
       <c r="L37">
-        <v>0.43118969448194178</v>
+        <v>0.4321000567596132</v>
       </c>
       <c r="M37">
-        <v>0.41683479797810641</v>
+        <v>0.415287584251967</v>
       </c>
       <c r="N37">
-        <v>0.40899530211245633</v>
+        <v>0.4073292539337856</v>
       </c>
       <c r="O37">
-        <v>0.41310871130587978</v>
+        <v>0.4114355621102901</v>
       </c>
       <c r="P37">
-        <v>0.41909906236728661</v>
+        <v>0.4186998689878937</v>
       </c>
       <c r="Q37">
-        <v>0.42432778667777138</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>53</v>
+        <v>0.4227835561766074</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
+        </is>
       </c>
       <c r="B38">
-        <v>0.43718001389814942</v>
+        <v>0.434463011577629</v>
       </c>
       <c r="C38">
-        <v>0.49185390909952909</v>
+        <v>0.4903284480513979</v>
       </c>
       <c r="D38">
-        <v>0.51587614118972158</v>
+        <v>0.5148174076965356</v>
       </c>
       <c r="E38">
-        <v>0.51910922953744543</v>
+        <v>0.5164383460800862</v>
       </c>
       <c r="F38">
-        <v>0.50967137684381014</v>
+        <v>0.5075482192621941</v>
       </c>
       <c r="G38">
-        <v>0.5080798541430015</v>
+        <v>0.5062017787803151</v>
       </c>
       <c r="H38">
-        <v>0.50340134241248391</v>
+        <v>0.5007651915645199</v>
       </c>
       <c r="I38">
-        <v>0.514966807885884</v>
+        <v>0.5107376027277519</v>
       </c>
       <c r="J38">
-        <v>0.50760250583660582</v>
+        <v>0.5071314009604734</v>
       </c>
       <c r="K38">
-        <v>0.49070300461804328</v>
+        <v>0.491014098530089</v>
       </c>
       <c r="L38">
-        <v>0.43118595968876811</v>
+        <v>0.4306361298625336</v>
       </c>
       <c r="M38">
-        <v>0.41643171587572392</v>
+        <v>0.4156200397543156</v>
       </c>
       <c r="N38">
-        <v>0.40790423541440879</v>
+        <v>0.4092424058855842</v>
       </c>
       <c r="O38">
-        <v>0.41063648605199748</v>
+        <v>0.4089816624223877</v>
       </c>
       <c r="P38">
-        <v>0.41432953532611261</v>
+        <v>0.4130283335646277</v>
       </c>
       <c r="Q38">
-        <v>0.41700283631723167</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>54</v>
+        <v>0.416213021936542</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B39">
-        <v>0.43994810309489679</v>
+        <v>0.442801214480904</v>
       </c>
       <c r="C39">
-        <v>0.49114475432797072</v>
+        <v>0.4912726948847585</v>
       </c>
       <c r="D39">
-        <v>0.51560587551257064</v>
+        <v>0.5156405536007076</v>
       </c>
       <c r="E39">
-        <v>0.518989257715606</v>
+        <v>0.5177118820142909</v>
       </c>
       <c r="F39">
-        <v>0.51037429627866426</v>
+        <v>0.5095469707870496</v>
       </c>
       <c r="G39">
-        <v>0.50912967823907374</v>
+        <v>0.5066433611483705</v>
       </c>
       <c r="H39">
-        <v>0.5038709740753331</v>
+        <v>0.5020861995264393</v>
       </c>
       <c r="I39">
-        <v>0.51767392250486965</v>
+        <v>0.517158341536044</v>
       </c>
       <c r="J39">
-        <v>0.51062429655486397</v>
+        <v>0.5088482977620552</v>
       </c>
       <c r="K39">
-        <v>0.49636293651131519</v>
+        <v>0.4915255860956583</v>
       </c>
       <c r="L39">
-        <v>0.43902997746441591</v>
+        <v>0.4341614057188487</v>
       </c>
       <c r="M39">
-        <v>0.41977130435943488</v>
+        <v>0.4186004513305071</v>
       </c>
       <c r="N39">
-        <v>0.41258555137924879</v>
+        <v>0.4112328903304371</v>
       </c>
       <c r="O39">
-        <v>0.41245929424301969</v>
+        <v>0.4118124267041404</v>
       </c>
       <c r="P39">
-        <v>0.41795894293463343</v>
+        <v>0.4170865294193499</v>
       </c>
       <c r="Q39">
-        <v>0.4179261739865095</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>55</v>
+        <v>0.4190880015407247</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B40">
-        <v>0.43617923304074158</v>
+        <v>0.4326412051433705</v>
       </c>
       <c r="C40">
-        <v>0.49132195601087669</v>
+        <v>0.4914679840479939</v>
       </c>
       <c r="D40">
-        <v>0.51607971998730251</v>
+        <v>0.5145031375959507</v>
       </c>
       <c r="E40">
-        <v>0.51868511141736573</v>
+        <v>0.5164567996098013</v>
       </c>
       <c r="F40">
-        <v>0.51053820394011684</v>
+        <v>0.5081236177675216</v>
       </c>
       <c r="G40">
-        <v>0.50792153348892266</v>
+        <v>0.5062949467376919</v>
       </c>
       <c r="H40">
-        <v>0.50218017154936001</v>
+        <v>0.5019757988356367</v>
       </c>
       <c r="I40">
-        <v>0.51406514699014705</v>
+        <v>0.5134278929027347</v>
       </c>
       <c r="J40">
-        <v>0.50729649122259957</v>
+        <v>0.5092435226983457</v>
       </c>
       <c r="K40">
-        <v>0.49294504738383632</v>
+        <v>0.493176179292135</v>
       </c>
       <c r="L40">
-        <v>0.43402340242107801</v>
+        <v>0.4321684981992661</v>
       </c>
       <c r="M40">
-        <v>0.4198169640823281</v>
+        <v>0.4179368629182468</v>
       </c>
       <c r="N40">
-        <v>0.41429228689242131</v>
+        <v>0.4105369878503089</v>
       </c>
       <c r="O40">
-        <v>0.40908676654574322</v>
+        <v>0.4057082337998271</v>
       </c>
       <c r="P40">
-        <v>0.4093442655300954</v>
+        <v>0.4075042371571334</v>
       </c>
       <c r="Q40">
-        <v>0.40490826538171509</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>56</v>
+        <v>0.4011991971017327</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B41">
-        <v>0.49657738538539742</v>
+        <v>0.494874193620455</v>
       </c>
       <c r="C41">
-        <v>0.49222585416460479</v>
+        <v>0.4924203644872667</v>
       </c>
       <c r="D41">
-        <v>0.52332433146736523</v>
+        <v>0.5217934937190254</v>
       </c>
       <c r="E41">
-        <v>0.50906668617566686</v>
+        <v>0.5085114632571094</v>
       </c>
       <c r="F41">
-        <v>0.49972513811122282</v>
+        <v>0.5012347342924377</v>
       </c>
       <c r="G41">
-        <v>0.50548140108027328</v>
+        <v>0.5054749210965294</v>
       </c>
       <c r="H41">
-        <v>0.50017344702703048</v>
+        <v>0.5003411552269119</v>
       </c>
       <c r="I41">
-        <v>0.4744165997757086</v>
+        <v>0.4772035394544742</v>
       </c>
       <c r="J41">
-        <v>0.46854138105696791</v>
+        <v>0.4709760832453626</v>
       </c>
       <c r="K41">
-        <v>0.47085752504462641</v>
+        <v>0.4711726534683842</v>
       </c>
       <c r="L41">
-        <v>0.46518781186497088</v>
+        <v>0.4626838806591779</v>
       </c>
       <c r="M41">
-        <v>0.46615067138694632</v>
+        <v>0.4648881245063625</v>
       </c>
       <c r="N41">
-        <v>0.47734616938363877</v>
+        <v>0.4754947109413313</v>
       </c>
       <c r="O41">
-        <v>0.46750739948486991</v>
+        <v>0.4653813442918535</v>
       </c>
       <c r="P41">
-        <v>0.46083527686009101</v>
+        <v>0.4584350475648298</v>
       </c>
       <c r="Q41">
-        <v>0.45850880644371578</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>57</v>
+        <v>0.4557029324461664</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
+        </is>
       </c>
       <c r="B42">
-        <v>0.44812600424643118</v>
+        <v>0.4486062971985421</v>
       </c>
       <c r="C42">
-        <v>0.4925084287613421</v>
+        <v>0.4923577002975529</v>
       </c>
       <c r="D42">
-        <v>0.520062409492273</v>
+        <v>0.5187770156792278</v>
       </c>
       <c r="E42">
-        <v>0.51408087920182721</v>
+        <v>0.5127085743676015</v>
       </c>
       <c r="F42">
-        <v>0.4918188877435663</v>
+        <v>0.489347394190875</v>
       </c>
       <c r="G42">
-        <v>0.47525420351780739</v>
+        <v>0.4727215960185741</v>
       </c>
       <c r="H42">
-        <v>0.44953773398160429</v>
+        <v>0.4486523919370021</v>
       </c>
       <c r="I42">
-        <v>0.41164767687981407</v>
+        <v>0.414883946780856</v>
       </c>
       <c r="J42">
-        <v>0.41657019606002649</v>
+        <v>0.4178581579349747</v>
       </c>
       <c r="K42">
-        <v>0.42940360630480651</v>
+        <v>0.4306067095756834</v>
       </c>
       <c r="L42">
-        <v>0.43554866815526477</v>
+        <v>0.436728734207043</v>
       </c>
       <c r="M42">
-        <v>0.43400192337402987</v>
+        <v>0.4360131279245923</v>
       </c>
       <c r="N42">
-        <v>0.43189452197807637</v>
+        <v>0.4322381550095653</v>
       </c>
       <c r="O42">
-        <v>0.41799052947780091</v>
+        <v>0.422187776107641</v>
       </c>
       <c r="P42">
-        <v>0.41037550802965073</v>
+        <v>0.4143047475534237</v>
       </c>
       <c r="Q42">
-        <v>0.40937913091286549</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>58</v>
+        <v>0.4126271847350352</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B43">
-        <v>0.44613736891035011</v>
+        <v>0.4485102467968233</v>
       </c>
       <c r="C43">
-        <v>0.49174267487546808</v>
+        <v>0.4913558842646973</v>
       </c>
       <c r="D43">
-        <v>0.51715950457398663</v>
+        <v>0.5163582408469914</v>
       </c>
       <c r="E43">
-        <v>0.50944059741945324</v>
+        <v>0.5078525634525689</v>
       </c>
       <c r="F43">
-        <v>0.48538601226152722</v>
+        <v>0.4873444968869723</v>
       </c>
       <c r="G43">
-        <v>0.47836325004114638</v>
+        <v>0.4781244729908391</v>
       </c>
       <c r="H43">
-        <v>0.45732046670301918</v>
+        <v>0.455589227899151</v>
       </c>
       <c r="I43">
-        <v>0.4229188708732749</v>
+        <v>0.4231298551426253</v>
       </c>
       <c r="J43">
-        <v>0.42075752966363411</v>
+        <v>0.4197885992038056</v>
       </c>
       <c r="K43">
-        <v>0.41876409680473808</v>
+        <v>0.4204161604680247</v>
       </c>
       <c r="L43">
-        <v>0.41722650842595399</v>
+        <v>0.4186249741809022</v>
       </c>
       <c r="M43">
-        <v>0.41819387443773121</v>
+        <v>0.4193631958267206</v>
       </c>
       <c r="N43">
-        <v>0.40758310402858688</v>
+        <v>0.4099379532417916</v>
       </c>
       <c r="O43">
-        <v>0.40477411163841848</v>
+        <v>0.4068110020105177</v>
       </c>
       <c r="P43">
-        <v>0.4053557332708877</v>
+        <v>0.4067115409752927</v>
       </c>
       <c r="Q43">
-        <v>0.40445368203113391</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>59</v>
+        <v>0.4036817081875954</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
+        </is>
       </c>
       <c r="B44">
-        <v>0.49543168677728983</v>
+        <v>0.4927869029834982</v>
       </c>
       <c r="C44">
-        <v>0.49771626442410383</v>
+        <v>0.4993311404562504</v>
       </c>
       <c r="D44">
-        <v>0.50459151408307201</v>
+        <v>0.5047517366411747</v>
       </c>
       <c r="E44">
-        <v>0.48269248911219442</v>
+        <v>0.4809103946363611</v>
       </c>
       <c r="F44">
-        <v>0.49142346016417671</v>
+        <v>0.4917456500384156</v>
       </c>
       <c r="G44">
-        <v>0.46363218607088691</v>
+        <v>0.462858428706667</v>
       </c>
       <c r="H44">
-        <v>0.44862172575208842</v>
+        <v>0.4445306379878873</v>
       </c>
       <c r="I44">
-        <v>0.45640563446812837</v>
+        <v>0.4556310128060565</v>
       </c>
       <c r="J44">
-        <v>0.46743575752583588</v>
+        <v>0.4681770311929872</v>
       </c>
       <c r="K44">
-        <v>0.4634251586758531</v>
+        <v>0.4628268408235265</v>
       </c>
       <c r="L44">
-        <v>0.44947711041129002</v>
+        <v>0.4500742666841356</v>
       </c>
       <c r="M44">
-        <v>0.44685850341934069</v>
+        <v>0.447092571481614</v>
       </c>
       <c r="N44">
-        <v>0.43957928192634438</v>
+        <v>0.4391842232802353</v>
       </c>
       <c r="O44">
-        <v>0.44206837150862283</v>
+        <v>0.4411535179511162</v>
       </c>
       <c r="P44">
-        <v>0.44998188174013531</v>
+        <v>0.4490677562247735</v>
       </c>
       <c r="Q44">
-        <v>0.46483817645171649</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>60</v>
+        <v>0.4623199175892326</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(1,3,5)_</t>
+        </is>
       </c>
       <c r="B45">
-        <v>0.49466773478960779</v>
+        <v>0.4949621359408478</v>
       </c>
       <c r="C45">
-        <v>0.49368241739320301</v>
+        <v>0.4943494887825846</v>
       </c>
       <c r="D45">
-        <v>0.53279053347593952</v>
+        <v>0.5335507325477565</v>
       </c>
       <c r="E45">
-        <v>0.51571958935246498</v>
+        <v>0.5155293781133745</v>
       </c>
       <c r="F45">
-        <v>0.52758014918674634</v>
+        <v>0.5279636679966681</v>
       </c>
       <c r="G45">
-        <v>0.51008721368411925</v>
+        <v>0.5108344547401212</v>
       </c>
       <c r="H45">
-        <v>0.50931456847295087</v>
+        <v>0.5101213032292774</v>
       </c>
       <c r="I45">
-        <v>0.49750949992589089</v>
+        <v>0.4990849112701474</v>
       </c>
       <c r="J45">
-        <v>0.4810429245832622</v>
+        <v>0.4823831350295499</v>
       </c>
       <c r="K45">
-        <v>0.49028925474800439</v>
+        <v>0.4915628989507057</v>
       </c>
       <c r="L45">
-        <v>0.49843229721336929</v>
+        <v>0.4990324819854955</v>
       </c>
       <c r="M45">
-        <v>0.49747979079897631</v>
+        <v>0.4955949313178721</v>
       </c>
       <c r="N45">
-        <v>0.50333710001303489</v>
+        <v>0.5014116615635075</v>
       </c>
       <c r="O45">
-        <v>0.51612350499377058</v>
+        <v>0.5138030477420222</v>
       </c>
       <c r="P45">
-        <v>0.51613247493395586</v>
+        <v>0.513655309809165</v>
       </c>
       <c r="Q45">
-        <v>0.51546106593698193</v>
-      </c>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>61</v>
+        <v>0.513943600520065</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B46">
-        <v>0.42624874330133389</v>
+        <v>0.4236746693200892</v>
       </c>
       <c r="C46">
-        <v>0.48539279831221338</v>
+        <v>0.485675223519033</v>
       </c>
       <c r="D46">
-        <v>0.50488867893585232</v>
+        <v>0.5037899180747631</v>
       </c>
       <c r="E46">
-        <v>0.52854116689561548</v>
+        <v>0.5295479411049961</v>
       </c>
       <c r="F46">
-        <v>0.47668086012310412</v>
+        <v>0.4727118470268732</v>
       </c>
       <c r="G46">
-        <v>0.44770049209262308</v>
+        <v>0.4451079124710843</v>
       </c>
       <c r="H46">
-        <v>0.43370037118385579</v>
+        <v>0.4353586767428674</v>
       </c>
       <c r="I46">
-        <v>0.40239365080658279</v>
+        <v>0.3996078482817358</v>
       </c>
       <c r="J46">
-        <v>0.40112085592722291</v>
+        <v>0.3987262880635674</v>
       </c>
       <c r="K46">
-        <v>0.40372059429025098</v>
+        <v>0.4037779607698051</v>
       </c>
       <c r="L46">
-        <v>0.3896475371437057</v>
+        <v>0.3896916986284102</v>
       </c>
       <c r="M46">
-        <v>0.38628794886047318</v>
+        <v>0.3873490308958106</v>
       </c>
       <c r="N46">
-        <v>0.39021083246409299</v>
+        <v>0.3902863868372032</v>
       </c>
       <c r="O46">
-        <v>0.39050266212095069</v>
+        <v>0.3920645019299708</v>
       </c>
       <c r="P46">
-        <v>0.39241210756091582</v>
+        <v>0.391690769676685</v>
       </c>
       <c r="Q46">
-        <v>0.3969237229697033</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>62</v>
+        <v>0.3977673139452922</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
+        </is>
       </c>
       <c r="B47">
-        <v>0.45055163023956929</v>
+        <v>0.4461287251535243</v>
       </c>
       <c r="C47">
-        <v>0.488086177493743</v>
+        <v>0.4879568783131614</v>
       </c>
       <c r="D47">
-        <v>0.50232250858636607</v>
+        <v>0.5044568926765928</v>
       </c>
       <c r="E47">
-        <v>0.49542167435530099</v>
+        <v>0.4998103560497642</v>
       </c>
       <c r="F47">
-        <v>0.46867806141813279</v>
+        <v>0.4714453308058135</v>
       </c>
       <c r="G47">
-        <v>0.43381821417902661</v>
+        <v>0.4344669798905135</v>
       </c>
       <c r="H47">
-        <v>0.42615995378202409</v>
+        <v>0.4277669207017423</v>
       </c>
       <c r="I47">
-        <v>0.41183468582786847</v>
+        <v>0.4118769404773597</v>
       </c>
       <c r="J47">
-        <v>0.40865534387325192</v>
+        <v>0.408499247386427</v>
       </c>
       <c r="K47">
-        <v>0.41629339991974051</v>
+        <v>0.4169786405412757</v>
       </c>
       <c r="L47">
-        <v>0.41047271436286942</v>
+        <v>0.4112056673138204</v>
       </c>
       <c r="M47">
-        <v>0.40673137767093248</v>
+        <v>0.4072445446686773</v>
       </c>
       <c r="N47">
-        <v>0.40859391315205917</v>
+        <v>0.4090937610292969</v>
       </c>
       <c r="O47">
-        <v>0.41711468261326401</v>
+        <v>0.4178812621640152</v>
       </c>
       <c r="P47">
-        <v>0.42595782858536152</v>
+        <v>0.4249906681479446</v>
       </c>
       <c r="Q47">
-        <v>0.4317217570376925</v>
+        <v>0.4324006526340856</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:Q18 C20:Q47 C19:L19 N19:Q19">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="top10" dxfId="1" priority="1" bottom="1" rank="10"/>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/ROSA_vitaSPEC/Results/test_pretraitements/ratio.alpha.beta/Resultats_ratio.alpha.beta_moy_RMSEP.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/ratio.alpha.beta/Resultats_ratio.alpha.beta_moy_RMSEP.xlsx
@@ -1,21 +1,211 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U108-N806\Documents\STAGE_M2_ROSA_NIRS\VitaSPEC\vitaspec_R\ROSA_vitaSPEC\Results\test_pretraitements\ratio.alpha.beta\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+  <si>
+    <t>Pretraitement</t>
+  </si>
+  <si>
+    <t>RMSEP_glo</t>
+  </si>
+  <si>
+    <t>LV0_RMSEP</t>
+  </si>
+  <si>
+    <t>LV1_RMSEP</t>
+  </si>
+  <si>
+    <t>LV2_RMSEP</t>
+  </si>
+  <si>
+    <t>LV3_RMSEP</t>
+  </si>
+  <si>
+    <t>LV4_RMSEP</t>
+  </si>
+  <si>
+    <t>LV5_RMSEP</t>
+  </si>
+  <si>
+    <t>LV6_RMSEP</t>
+  </si>
+  <si>
+    <t>LV7_RMSEP</t>
+  </si>
+  <si>
+    <t>LV8_RMSEP</t>
+  </si>
+  <si>
+    <t>LV9_RMSEP</t>
+  </si>
+  <si>
+    <t>LV10_RMSEP</t>
+  </si>
+  <si>
+    <t>LV11_RMSEP</t>
+  </si>
+  <si>
+    <t>LV12_RMSEP</t>
+  </si>
+  <si>
+    <t>LV13_RMSEP</t>
+  </si>
+  <si>
+    <t>LV14_RMSEP</t>
+  </si>
+  <si>
+    <t>LV15_RMSEP</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1000,1)_snv_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_msc_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_snv_sder_c(1,3,5)_</t>
+  </si>
+  <si>
+    <t>adj_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,11 +253,19 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -109,7 +307,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -141,9 +339,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -175,6 +374,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -350,2628 +550,2436 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q47"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:R43"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="51.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="12" width="12" bestFit="1" customWidth="1"/>
+    <col min="13" max="18" width="12.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Pretraitement</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>RMSEP_glo</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>LV1_RMSEP</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>LV2_RMSEP</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>LV3_RMSEP</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>LV4_RMSEP</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>LV5_RMSEP</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>LV6_RMSEP</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>LV7_RMSEP</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>LV8_RMSEP</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>LV9_RMSEP</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>LV10_RMSEP</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>LV11_RMSEP</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>LV12_RMSEP</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>LV13_RMSEP</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>LV14_RMSEP</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>LV15_RMSEP</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1000,1)_snv_</t>
-        </is>
+    <row r="1" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>18</v>
       </c>
       <c r="B2">
-        <v>0.4226742440226443</v>
+        <v>0.41842844126741657</v>
       </c>
       <c r="C2">
-        <v>0.4888192059822374</v>
+        <v>0.48594555921399668</v>
       </c>
       <c r="D2">
-        <v>0.4939198133694742</v>
+        <v>0.48972842429048552</v>
       </c>
       <c r="E2">
-        <v>0.4954290671558664</v>
+        <v>0.49421525964178731</v>
       </c>
       <c r="F2">
-        <v>0.4961688360137458</v>
+        <v>0.4956173537110643</v>
       </c>
       <c r="G2">
-        <v>0.4947404259449011</v>
+        <v>0.49594335816417551</v>
       </c>
       <c r="H2">
-        <v>0.4971004001245919</v>
+        <v>0.49578859301752409</v>
       </c>
       <c r="I2">
-        <v>0.4826085635895935</v>
+        <v>0.49612088007914962</v>
       </c>
       <c r="J2">
-        <v>0.4606257657292137</v>
+        <v>0.48060378253189467</v>
       </c>
       <c r="K2">
-        <v>0.4698804531704709</v>
+        <v>0.4586448263593072</v>
       </c>
       <c r="L2">
-        <v>0.4611261729777885</v>
+        <v>0.46947524655997558</v>
       </c>
       <c r="M2">
-        <v>0.4358471295989863</v>
+        <v>0.45722070470630122</v>
       </c>
       <c r="N2">
-        <v>0.4268531836722555</v>
+        <v>0.43452404954275958</v>
       </c>
       <c r="O2">
-        <v>0.4024302078339416</v>
+        <v>0.4247318496996772</v>
       </c>
       <c r="P2">
-        <v>0.379546689683589</v>
+        <v>0.40144362173557491</v>
       </c>
       <c r="Q2">
-        <v>0.3652001878663406</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.37787961633011091</v>
+      </c>
+      <c r="R2">
+        <v>0.36580497996368488</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>19</v>
       </c>
       <c r="B3">
-        <v>0.4372841819775964</v>
+        <v>0.4371841300768296</v>
       </c>
       <c r="C3">
-        <v>0.4864608223713254</v>
+        <v>0.48594555921399668</v>
       </c>
       <c r="D3">
-        <v>0.4924185240634107</v>
+        <v>0.48693007513739578</v>
       </c>
       <c r="E3">
-        <v>0.5209343838015882</v>
+        <v>0.49234430812624719</v>
       </c>
       <c r="F3">
-        <v>0.4759541854591819</v>
+        <v>0.52209718826700713</v>
       </c>
       <c r="G3">
-        <v>0.4511037545581915</v>
+        <v>0.47808825727616638</v>
       </c>
       <c r="H3">
-        <v>0.4373632596191334</v>
+        <v>0.45627951564534258</v>
       </c>
       <c r="I3">
-        <v>0.425696472017711</v>
+        <v>0.43841114400527947</v>
       </c>
       <c r="J3">
-        <v>0.4209984155551564</v>
+        <v>0.42434008656274602</v>
       </c>
       <c r="K3">
-        <v>0.4030933241578818</v>
+        <v>0.41992371786066629</v>
       </c>
       <c r="L3">
-        <v>0.3904016543640056</v>
+        <v>0.40261697582974082</v>
       </c>
       <c r="M3">
-        <v>0.3906610689566032</v>
+        <v>0.38976389180599308</v>
       </c>
       <c r="N3">
-        <v>0.389201213020162</v>
+        <v>0.39080430403228661</v>
       </c>
       <c r="O3">
-        <v>0.3969458648841259</v>
+        <v>0.38896976020995699</v>
       </c>
       <c r="P3">
-        <v>0.3967466845188405</v>
+        <v>0.39851132582487903</v>
       </c>
       <c r="Q3">
-        <v>0.3893727813626784</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_msc_</t>
-        </is>
+        <v>0.40002804347199222</v>
+      </c>
+      <c r="R3">
+        <v>0.39124743013102831</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>20</v>
       </c>
       <c r="B4">
-        <v>0.4288861114333317</v>
+        <v>0.4265484658251012</v>
       </c>
       <c r="C4">
-        <v>0.4895273378388955</v>
+        <v>0.48594555921399668</v>
       </c>
       <c r="D4">
-        <v>0.4920298717348165</v>
+        <v>0.4887279150808983</v>
       </c>
       <c r="E4">
-        <v>0.5099011746786603</v>
+        <v>0.49245718756941748</v>
       </c>
       <c r="F4">
-        <v>0.5083361640715831</v>
+        <v>0.51222723010393378</v>
       </c>
       <c r="G4">
-        <v>0.5218070765171465</v>
+        <v>0.5127307783848063</v>
       </c>
       <c r="H4">
-        <v>0.491004811136202</v>
+        <v>0.52836909810507371</v>
       </c>
       <c r="I4">
-        <v>0.456922466791794</v>
+        <v>0.49587054899704591</v>
       </c>
       <c r="J4">
-        <v>0.4526162010971782</v>
+        <v>0.45939021333486307</v>
       </c>
       <c r="K4">
-        <v>0.4466113847803301</v>
+        <v>0.45342733203679259</v>
       </c>
       <c r="L4">
-        <v>0.4309764779854283</v>
+        <v>0.44936805043665429</v>
       </c>
       <c r="M4">
-        <v>0.4101806487100563</v>
+        <v>0.4292430554837196</v>
       </c>
       <c r="N4">
-        <v>0.3926886297450659</v>
+        <v>0.41001135216232298</v>
       </c>
       <c r="O4">
-        <v>0.3796684462480264</v>
+        <v>0.39278834158983528</v>
       </c>
       <c r="P4">
-        <v>0.3777417201385767</v>
+        <v>0.38141044296596638</v>
       </c>
       <c r="Q4">
-        <v>0.3788010070208745</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.37744566342548008</v>
+      </c>
+      <c r="R4">
+        <v>0.37946104239979228</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>21</v>
       </c>
       <c r="B5">
-        <v>0.3965240521093475</v>
+        <v>0.39745522524434701</v>
       </c>
       <c r="C5">
-        <v>0.4868488755834224</v>
+        <v>0.48594555921399668</v>
       </c>
       <c r="D5">
-        <v>0.4989030846696772</v>
+        <v>0.48755636714605632</v>
       </c>
       <c r="E5">
-        <v>0.4991494597594291</v>
+        <v>0.49926180815580612</v>
       </c>
       <c r="F5">
-        <v>0.5113773547258474</v>
+        <v>0.50173637327541654</v>
       </c>
       <c r="G5">
-        <v>0.4595755307192697</v>
+        <v>0.51252228512701281</v>
       </c>
       <c r="H5">
-        <v>0.432034583245052</v>
+        <v>0.46017539656023693</v>
       </c>
       <c r="I5">
-        <v>0.4198513834017426</v>
+        <v>0.43561440855788108</v>
       </c>
       <c r="J5">
-        <v>0.4020968333859172</v>
+        <v>0.42167006606136198</v>
       </c>
       <c r="K5">
-        <v>0.382578168759426</v>
+        <v>0.40312028272063499</v>
       </c>
       <c r="L5">
-        <v>0.3732070544697877</v>
+        <v>0.38189270953555338</v>
       </c>
       <c r="M5">
-        <v>0.3618529093119336</v>
+        <v>0.37030939516751959</v>
       </c>
       <c r="N5">
-        <v>0.3623118425558357</v>
+        <v>0.35753367984825313</v>
       </c>
       <c r="O5">
-        <v>0.3693110305130579</v>
+        <v>0.35771727660731462</v>
       </c>
       <c r="P5">
-        <v>0.375602924806527</v>
+        <v>0.3644125221427777</v>
       </c>
       <c r="Q5">
-        <v>0.3820836641704876</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
-        </is>
+        <v>0.37199919475905902</v>
+      </c>
+      <c r="R5">
+        <v>0.37887044019806337</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>22</v>
       </c>
       <c r="B6">
-        <v>0.3773849962458408</v>
+        <v>0.3758144351961572</v>
       </c>
       <c r="C6">
-        <v>0.4873484012094193</v>
+        <v>0.48594555921399668</v>
       </c>
       <c r="D6">
-        <v>0.4989234372983741</v>
+        <v>0.4876195117684492</v>
       </c>
       <c r="E6">
-        <v>0.4970582673545261</v>
+        <v>0.49943738837591339</v>
       </c>
       <c r="F6">
-        <v>0.4945546835260101</v>
+        <v>0.50159338472441772</v>
       </c>
       <c r="G6">
-        <v>0.4409719097248134</v>
+        <v>0.49765582273427961</v>
       </c>
       <c r="H6">
-        <v>0.404688369015001</v>
+        <v>0.43930224128583001</v>
       </c>
       <c r="I6">
-        <v>0.3915713381815271</v>
+        <v>0.4062477587801826</v>
       </c>
       <c r="J6">
-        <v>0.3708316797016893</v>
+        <v>0.39184879690863861</v>
       </c>
       <c r="K6">
-        <v>0.3576917498319881</v>
+        <v>0.36996165771130352</v>
       </c>
       <c r="L6">
-        <v>0.3498784022900627</v>
+        <v>0.3556679492582453</v>
       </c>
       <c r="M6">
-        <v>0.3440611582453303</v>
+        <v>0.34926949251305961</v>
       </c>
       <c r="N6">
-        <v>0.3426460995760416</v>
+        <v>0.34287488244209052</v>
       </c>
       <c r="O6">
-        <v>0.3447274919009714</v>
+        <v>0.34067418299801389</v>
       </c>
       <c r="P6">
-        <v>0.3427312516525445</v>
+        <v>0.34346910650294998</v>
       </c>
       <c r="Q6">
-        <v>0.3467130054281706</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_</t>
-        </is>
+        <v>0.34195064315898188</v>
+      </c>
+      <c r="R6">
+        <v>0.34763702668618501</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>23</v>
       </c>
       <c r="B7">
-        <v>0.4301065386006754</v>
+        <v>0.42639350381070362</v>
       </c>
       <c r="C7">
-        <v>0.4903685148416082</v>
+        <v>0.48594555921399668</v>
       </c>
       <c r="D7">
-        <v>0.4940547294511766</v>
+        <v>0.48985574931640458</v>
       </c>
       <c r="E7">
-        <v>0.5147069630665639</v>
+        <v>0.49350061056118039</v>
       </c>
       <c r="F7">
-        <v>0.5165627611452566</v>
+        <v>0.51396064326894619</v>
       </c>
       <c r="G7">
-        <v>0.5269365335468842</v>
+        <v>0.51672936153378179</v>
       </c>
       <c r="H7">
-        <v>0.5240584056348191</v>
+        <v>0.52700061358016392</v>
       </c>
       <c r="I7">
-        <v>0.4877829034660921</v>
+        <v>0.52663239989754962</v>
       </c>
       <c r="J7">
-        <v>0.4578790623974783</v>
+        <v>0.49020783144325908</v>
       </c>
       <c r="K7">
-        <v>0.4577979918215447</v>
+        <v>0.4602840704059955</v>
       </c>
       <c r="L7">
-        <v>0.4477089965404905</v>
+        <v>0.46045659973140768</v>
       </c>
       <c r="M7">
-        <v>0.4246782970642763</v>
+        <v>0.44777444692530638</v>
       </c>
       <c r="N7">
-        <v>0.404253345971022</v>
+        <v>0.42476728662181662</v>
       </c>
       <c r="O7">
-        <v>0.3888965093752614</v>
+        <v>0.4036194213400261</v>
       </c>
       <c r="P7">
-        <v>0.3791835166871299</v>
+        <v>0.38666363369745621</v>
       </c>
       <c r="Q7">
-        <v>0.3745246469420439</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
-        </is>
+        <v>0.37614383423999731</v>
+      </c>
+      <c r="R7">
+        <v>0.37158739716006078</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>24</v>
       </c>
       <c r="B8">
-        <v>0.4101705403975482</v>
+        <v>0.41387947892573229</v>
       </c>
       <c r="C8">
-        <v>0.4881821792959191</v>
+        <v>0.48594555921399668</v>
       </c>
       <c r="D8">
-        <v>0.4914198781097748</v>
+        <v>0.48876214825963221</v>
       </c>
       <c r="E8">
-        <v>0.5088882716768263</v>
+        <v>0.49217686033869013</v>
       </c>
       <c r="F8">
-        <v>0.5164976949109451</v>
+        <v>0.50950008272538494</v>
       </c>
       <c r="G8">
-        <v>0.5002131556379041</v>
+        <v>0.51520482409924384</v>
       </c>
       <c r="H8">
-        <v>0.4778092685358511</v>
+        <v>0.50224966005789295</v>
       </c>
       <c r="I8">
-        <v>0.46290947884958</v>
+        <v>0.48015004486971502</v>
       </c>
       <c r="J8">
-        <v>0.4390433922451742</v>
+        <v>0.4661736316489315</v>
       </c>
       <c r="K8">
-        <v>0.4264940217581807</v>
+        <v>0.44235129961232078</v>
       </c>
       <c r="L8">
-        <v>0.3941816708605062</v>
+        <v>0.4310709117663139</v>
       </c>
       <c r="M8">
-        <v>0.3900470935716154</v>
+        <v>0.39762185648146242</v>
       </c>
       <c r="N8">
-        <v>0.3767174891348817</v>
+        <v>0.39694677385277938</v>
       </c>
       <c r="O8">
-        <v>0.3648473255507672</v>
+        <v>0.38236634543048481</v>
       </c>
       <c r="P8">
-        <v>0.363716793952643</v>
+        <v>0.37037635119104761</v>
       </c>
       <c r="Q8">
-        <v>0.3667396287543956</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
-        </is>
+        <v>0.37067230457582051</v>
+      </c>
+      <c r="R8">
+        <v>0.37213497626246411</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>25</v>
       </c>
       <c r="B9">
-        <v>0.3871513585522323</v>
+        <v>0.38757925160500439</v>
       </c>
       <c r="C9">
-        <v>0.487421932026302</v>
+        <v>0.48594555921399668</v>
       </c>
       <c r="D9">
-        <v>0.4905668078456105</v>
+        <v>0.4882154350120973</v>
       </c>
       <c r="E9">
-        <v>0.5075376876647836</v>
+        <v>0.49190836444041619</v>
       </c>
       <c r="F9">
-        <v>0.5115652237231942</v>
+        <v>0.507507817299922</v>
       </c>
       <c r="G9">
-        <v>0.4996270893921387</v>
+        <v>0.51362201501148208</v>
       </c>
       <c r="H9">
-        <v>0.4764526896287188</v>
+        <v>0.50021150711931506</v>
       </c>
       <c r="I9">
-        <v>0.4620243340064498</v>
+        <v>0.47844321883056462</v>
       </c>
       <c r="J9">
-        <v>0.4378661573001416</v>
+        <v>0.46573956492564872</v>
       </c>
       <c r="K9">
-        <v>0.4273175357086308</v>
+        <v>0.44222210850813631</v>
       </c>
       <c r="L9">
-        <v>0.3836553136211127</v>
+        <v>0.43085783488759438</v>
       </c>
       <c r="M9">
-        <v>0.3789089010751477</v>
+        <v>0.38371096051455589</v>
       </c>
       <c r="N9">
-        <v>0.3678343341588176</v>
+        <v>0.38133077608557181</v>
       </c>
       <c r="O9">
-        <v>0.3574541197324786</v>
+        <v>0.37014129065588047</v>
       </c>
       <c r="P9">
-        <v>0.355509927471088</v>
+        <v>0.35908419919840051</v>
       </c>
       <c r="Q9">
-        <v>0.3543739906704627</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
-        </is>
+        <v>0.35563641968890097</v>
+      </c>
+      <c r="R9">
+        <v>0.35536721674708949</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>26</v>
       </c>
       <c r="B10">
-        <v>0.392838093299285</v>
+        <v>0.39364474379292302</v>
       </c>
       <c r="C10">
-        <v>0.4882908567812589</v>
+        <v>0.48594555921399668</v>
       </c>
       <c r="D10">
-        <v>0.4920483125289776</v>
+        <v>0.48782123876697092</v>
       </c>
       <c r="E10">
-        <v>0.5083425796290446</v>
+        <v>0.49140228515904361</v>
       </c>
       <c r="F10">
-        <v>0.5120823773685561</v>
+        <v>0.50951380451537154</v>
       </c>
       <c r="G10">
-        <v>0.4991059693850192</v>
+        <v>0.51405537981297766</v>
       </c>
       <c r="H10">
-        <v>0.4798197005524167</v>
+        <v>0.50227223690886025</v>
       </c>
       <c r="I10">
-        <v>0.4658804505790127</v>
+        <v>0.48035667811901922</v>
       </c>
       <c r="J10">
-        <v>0.4404598336859399</v>
+        <v>0.46613205299469151</v>
       </c>
       <c r="K10">
-        <v>0.4298169808290867</v>
+        <v>0.44274019427345679</v>
       </c>
       <c r="L10">
-        <v>0.3860132288424725</v>
+        <v>0.43312759477384022</v>
       </c>
       <c r="M10">
-        <v>0.3854794277952696</v>
+        <v>0.3877263198932589</v>
       </c>
       <c r="N10">
-        <v>0.3730679239704072</v>
+        <v>0.3865239865384722</v>
       </c>
       <c r="O10">
-        <v>0.361386021292406</v>
+        <v>0.37536901918126608</v>
       </c>
       <c r="P10">
-        <v>0.3605391456939658</v>
+        <v>0.36577820602566108</v>
       </c>
       <c r="Q10">
-        <v>0.3584173634623262</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-        </is>
+        <v>0.36215702117807042</v>
+      </c>
+      <c r="R10">
+        <v>0.36062969117831822</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>27</v>
       </c>
       <c r="B11">
-        <v>0.3883563894556256</v>
+        <v>0.38884906665697871</v>
       </c>
       <c r="C11">
-        <v>0.4880611176900764</v>
+        <v>0.48594555921399668</v>
       </c>
       <c r="D11">
-        <v>0.4919160922398127</v>
+        <v>0.48901373128614628</v>
       </c>
       <c r="E11">
-        <v>0.5099102285141707</v>
+        <v>0.49290653765833869</v>
       </c>
       <c r="F11">
-        <v>0.5162591525731344</v>
+        <v>0.50916115347444191</v>
       </c>
       <c r="G11">
-        <v>0.504011721519167</v>
+        <v>0.51483230157151905</v>
       </c>
       <c r="H11">
-        <v>0.4781199644904124</v>
+        <v>0.50174759602858654</v>
       </c>
       <c r="I11">
-        <v>0.4677717242929246</v>
+        <v>0.48093501802019989</v>
       </c>
       <c r="J11">
-        <v>0.4405858716358577</v>
+        <v>0.46843057249887549</v>
       </c>
       <c r="K11">
-        <v>0.4293355337053935</v>
+        <v>0.44124696033102989</v>
       </c>
       <c r="L11">
-        <v>0.3838222127954313</v>
+        <v>0.43055742342171072</v>
       </c>
       <c r="M11">
-        <v>0.3800767387107911</v>
+        <v>0.38334103621729698</v>
       </c>
       <c r="N11">
-        <v>0.3674829915440919</v>
+        <v>0.38029935117437219</v>
       </c>
       <c r="O11">
-        <v>0.3577822566691834</v>
+        <v>0.3693065556607229</v>
       </c>
       <c r="P11">
-        <v>0.3576609150351822</v>
+        <v>0.35940793444064079</v>
       </c>
       <c r="Q11">
-        <v>0.3561003324177224</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.35833860565052239</v>
+      </c>
+      <c r="R11">
+        <v>0.35711197263987071</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>28</v>
       </c>
       <c r="B12">
-        <v>0.3883131918452451</v>
+        <v>0.38646480563156649</v>
       </c>
       <c r="C12">
-        <v>0.4867107790756526</v>
+        <v>0.48594555921399668</v>
       </c>
       <c r="D12">
-        <v>0.4989293126925561</v>
+        <v>0.48783329782282708</v>
       </c>
       <c r="E12">
-        <v>0.4992538611304946</v>
+        <v>0.50084869624457606</v>
       </c>
       <c r="F12">
-        <v>0.511824027407431</v>
+        <v>0.49574144298315681</v>
       </c>
       <c r="G12">
-        <v>0.4655836917252834</v>
+        <v>0.50770127734391268</v>
       </c>
       <c r="H12">
-        <v>0.4449622707075437</v>
+        <v>0.46087900506055768</v>
       </c>
       <c r="I12">
-        <v>0.4130956328628702</v>
+        <v>0.44059078651450517</v>
       </c>
       <c r="J12">
-        <v>0.3840867305744434</v>
+        <v>0.41325800473117269</v>
       </c>
       <c r="K12">
-        <v>0.369568759493616</v>
+        <v>0.38618551850338728</v>
       </c>
       <c r="L12">
-        <v>0.3601832738930018</v>
+        <v>0.37214742482831031</v>
       </c>
       <c r="M12">
-        <v>0.3483873676263139</v>
+        <v>0.36366203257066138</v>
       </c>
       <c r="N12">
-        <v>0.3482641729895672</v>
+        <v>0.35124928265076882</v>
       </c>
       <c r="O12">
-        <v>0.3529206144446361</v>
+        <v>0.35024354674875102</v>
       </c>
       <c r="P12">
-        <v>0.3600807506861182</v>
+        <v>0.35491355436373512</v>
       </c>
       <c r="Q12">
-        <v>0.3719125848332266</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
-        </is>
+        <v>0.36253351487236768</v>
+      </c>
+      <c r="R12">
+        <v>0.37468280639143559</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>29</v>
       </c>
       <c r="B13">
-        <v>0.4607882759562223</v>
+        <v>0.46320966441865091</v>
       </c>
       <c r="C13">
-        <v>0.4883000774622999</v>
+        <v>0.48594555921399668</v>
       </c>
       <c r="D13">
-        <v>0.5092289107394458</v>
+        <v>0.48715502804578559</v>
       </c>
       <c r="E13">
-        <v>0.5086789852588181</v>
+        <v>0.50946714811057392</v>
       </c>
       <c r="F13">
-        <v>0.5126827738803946</v>
+        <v>0.50780664545863141</v>
       </c>
       <c r="G13">
-        <v>0.5199881334011492</v>
+        <v>0.51184398539278153</v>
       </c>
       <c r="H13">
-        <v>0.4839479518496582</v>
+        <v>0.51916661609536219</v>
       </c>
       <c r="I13">
-        <v>0.4784562507663319</v>
+        <v>0.4860202655700141</v>
       </c>
       <c r="J13">
-        <v>0.4625220756543841</v>
+        <v>0.48011129148669363</v>
       </c>
       <c r="K13">
-        <v>0.4423429789255503</v>
+        <v>0.46414965423944848</v>
       </c>
       <c r="L13">
-        <v>0.4202856112290219</v>
+        <v>0.44337908439014978</v>
       </c>
       <c r="M13">
-        <v>0.4177377617199051</v>
+        <v>0.42340724252104261</v>
       </c>
       <c r="N13">
-        <v>0.4124419508884762</v>
+        <v>0.41752970180877041</v>
       </c>
       <c r="O13">
-        <v>0.4102437501285142</v>
+        <v>0.41059397069112469</v>
       </c>
       <c r="P13">
-        <v>0.4070102179237263</v>
+        <v>0.40827852078386262</v>
       </c>
       <c r="Q13">
-        <v>0.4124346261039041</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-        </is>
+        <v>0.40480801808644601</v>
+      </c>
+      <c r="R13">
+        <v>0.41061646623797993</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>30</v>
       </c>
       <c r="B14">
-        <v>0.3953138287066144</v>
+        <v>0.39426573573478019</v>
       </c>
       <c r="C14">
-        <v>0.4893154505095809</v>
+        <v>0.48594555921399668</v>
       </c>
       <c r="D14">
-        <v>0.4931909105682126</v>
+        <v>0.48909082083059607</v>
       </c>
       <c r="E14">
-        <v>0.5126181506509825</v>
+        <v>0.49331380709757172</v>
       </c>
       <c r="F14">
-        <v>0.5142659169602585</v>
+        <v>0.51294426645951474</v>
       </c>
       <c r="G14">
-        <v>0.5258147799872229</v>
+        <v>0.51350552962535934</v>
       </c>
       <c r="H14">
-        <v>0.5221974572355668</v>
+        <v>0.52342171237403323</v>
       </c>
       <c r="I14">
-        <v>0.4883678250316236</v>
+        <v>0.52106949628972099</v>
       </c>
       <c r="J14">
-        <v>0.4599823936867001</v>
+        <v>0.48756789744499668</v>
       </c>
       <c r="K14">
-        <v>0.459491378407535</v>
+        <v>0.4578847276714208</v>
       </c>
       <c r="L14">
-        <v>0.4482598203843563</v>
+        <v>0.45706661297676981</v>
       </c>
       <c r="M14">
-        <v>0.4196545990415571</v>
+        <v>0.44747736576775188</v>
       </c>
       <c r="N14">
-        <v>0.3874817458458058</v>
+        <v>0.41892761228226733</v>
       </c>
       <c r="O14">
-        <v>0.3757797804421176</v>
+        <v>0.38730347423556422</v>
       </c>
       <c r="P14">
-        <v>0.3659828411378018</v>
+        <v>0.37508676949999448</v>
       </c>
       <c r="Q14">
-        <v>0.3587647198537247</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-        </is>
+        <v>0.36586610666184199</v>
+      </c>
+      <c r="R14">
+        <v>0.36088746776451019</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>31</v>
       </c>
       <c r="B15">
-        <v>0.4004250533530196</v>
+        <v>0.40225304572761611</v>
       </c>
       <c r="C15">
-        <v>0.4902256665671618</v>
+        <v>0.48594555921399668</v>
       </c>
       <c r="D15">
-        <v>0.4943680519607214</v>
+        <v>0.4891360160101717</v>
       </c>
       <c r="E15">
-        <v>0.5138753660244602</v>
+        <v>0.49254749610802312</v>
       </c>
       <c r="F15">
-        <v>0.5148019205892108</v>
+        <v>0.51179711127637761</v>
       </c>
       <c r="G15">
-        <v>0.5264922364543307</v>
+        <v>0.51264142786705746</v>
       </c>
       <c r="H15">
-        <v>0.5250857473276089</v>
+        <v>0.52138132354845568</v>
       </c>
       <c r="I15">
-        <v>0.4903410052798544</v>
+        <v>0.51881024557971533</v>
       </c>
       <c r="J15">
-        <v>0.4622078185287672</v>
+        <v>0.48710925543105399</v>
       </c>
       <c r="K15">
-        <v>0.4650771721118666</v>
+        <v>0.46036010029314978</v>
       </c>
       <c r="L15">
-        <v>0.4502765355009604</v>
+        <v>0.45909358678196133</v>
       </c>
       <c r="M15">
-        <v>0.4226868651247893</v>
+        <v>0.44737243452525022</v>
       </c>
       <c r="N15">
-        <v>0.391316279284173</v>
+        <v>0.42292889035933451</v>
       </c>
       <c r="O15">
-        <v>0.3791216220194655</v>
+        <v>0.39303209675486078</v>
       </c>
       <c r="P15">
-        <v>0.3701925447916883</v>
+        <v>0.37984964148238431</v>
       </c>
       <c r="Q15">
-        <v>0.3624435010969766</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
-        </is>
+        <v>0.369396498510078</v>
+      </c>
+      <c r="R15">
+        <v>0.36453111915687958</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>32</v>
       </c>
       <c r="B16">
-        <v>0.3974855561162641</v>
+        <v>0.39719168161007562</v>
       </c>
       <c r="C16">
-        <v>0.4895097325757949</v>
+        <v>0.48594555921399668</v>
       </c>
       <c r="D16">
-        <v>0.4927301596249611</v>
+        <v>0.48911168532602889</v>
       </c>
       <c r="E16">
-        <v>0.5116941781750631</v>
+        <v>0.4930679587109788</v>
       </c>
       <c r="F16">
-        <v>0.5130986320139828</v>
+        <v>0.51224155285113904</v>
       </c>
       <c r="G16">
-        <v>0.5218424417430884</v>
+        <v>0.51260037059345487</v>
       </c>
       <c r="H16">
-        <v>0.5211519752193304</v>
+        <v>0.52316424972931486</v>
       </c>
       <c r="I16">
-        <v>0.4893204679386918</v>
+        <v>0.52009801256754529</v>
       </c>
       <c r="J16">
-        <v>0.4600577054194097</v>
+        <v>0.48880698455290489</v>
       </c>
       <c r="K16">
-        <v>0.4599235905623276</v>
+        <v>0.4593268089288734</v>
       </c>
       <c r="L16">
-        <v>0.4479405099106316</v>
+        <v>0.4579838180565533</v>
       </c>
       <c r="M16">
-        <v>0.4219075484090929</v>
+        <v>0.44773658939098487</v>
       </c>
       <c r="N16">
-        <v>0.388979612045709</v>
+        <v>0.4206971572982125</v>
       </c>
       <c r="O16">
-        <v>0.3746739632487901</v>
+        <v>0.38950485061243117</v>
       </c>
       <c r="P16">
-        <v>0.3638586758310591</v>
+        <v>0.37451999374486239</v>
       </c>
       <c r="Q16">
-        <v>0.3586979717624502</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-        </is>
+        <v>0.36484012638468438</v>
+      </c>
+      <c r="R16">
+        <v>0.35846925441534772</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>33</v>
       </c>
       <c r="B17">
-        <v>0.4104045971310095</v>
+        <v>0.40938775038778902</v>
       </c>
       <c r="C17">
-        <v>0.4887401369146407</v>
+        <v>0.48594555921399668</v>
       </c>
       <c r="D17">
-        <v>0.4932807825168768</v>
+        <v>0.49015415301697451</v>
       </c>
       <c r="E17">
-        <v>0.5131764034897524</v>
+        <v>0.49439227983013989</v>
       </c>
       <c r="F17">
-        <v>0.5136305713708033</v>
+        <v>0.51415244639709501</v>
       </c>
       <c r="G17">
-        <v>0.5220307660940554</v>
+        <v>0.51581316840275793</v>
       </c>
       <c r="H17">
-        <v>0.5214394778748255</v>
+        <v>0.52471145680574249</v>
       </c>
       <c r="I17">
-        <v>0.4887038450315182</v>
+        <v>0.52197484136113825</v>
       </c>
       <c r="J17">
-        <v>0.4623312731664756</v>
+        <v>0.49073068685748189</v>
       </c>
       <c r="K17">
-        <v>0.4639056355618676</v>
+        <v>0.46438703943827531</v>
       </c>
       <c r="L17">
-        <v>0.4526378575590124</v>
+        <v>0.4650555899639211</v>
       </c>
       <c r="M17">
-        <v>0.4300745274180369</v>
+        <v>0.45506445184160199</v>
       </c>
       <c r="N17">
-        <v>0.3996845179616462</v>
+        <v>0.43200190859196308</v>
       </c>
       <c r="O17">
-        <v>0.3878385367907338</v>
+        <v>0.40138541185117388</v>
       </c>
       <c r="P17">
-        <v>0.375702788929017</v>
+        <v>0.38796959576249851</v>
       </c>
       <c r="Q17">
-        <v>0.3681530381585914</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.37523835138458272</v>
+      </c>
+      <c r="R17">
+        <v>0.36728913148177611</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>34</v>
       </c>
       <c r="B18">
-        <v>0.3855395356175562</v>
+        <v>0.38571122911366967</v>
       </c>
       <c r="C18">
-        <v>0.486862566695043</v>
+        <v>0.48594555921399668</v>
       </c>
       <c r="D18">
-        <v>0.4994378150464132</v>
+        <v>0.48712109902383161</v>
       </c>
       <c r="E18">
-        <v>0.5004614798636534</v>
+        <v>0.5000051006374735</v>
       </c>
       <c r="F18">
-        <v>0.5136852789073979</v>
+        <v>0.50193884353679319</v>
       </c>
       <c r="G18">
-        <v>0.460299735609072</v>
+        <v>0.51286751019642263</v>
       </c>
       <c r="H18">
-        <v>0.4318494509050322</v>
+        <v>0.46380728393960302</v>
       </c>
       <c r="I18">
-        <v>0.4152367618698413</v>
+        <v>0.43293195206014629</v>
       </c>
       <c r="J18">
-        <v>0.3875024413356137</v>
+        <v>0.41608300521560332</v>
       </c>
       <c r="K18">
-        <v>0.3700852602912252</v>
+        <v>0.39082015330248132</v>
       </c>
       <c r="L18">
-        <v>0.364148721475167</v>
+        <v>0.3707911263570442</v>
       </c>
       <c r="M18">
-        <v>0.3541439330214875</v>
+        <v>0.36496833500904502</v>
       </c>
       <c r="N18">
-        <v>0.3520917805201244</v>
+        <v>0.35319325504247551</v>
       </c>
       <c r="O18">
-        <v>0.3607426982082129</v>
+        <v>0.35283613171208861</v>
       </c>
       <c r="P18">
-        <v>0.3687616051926433</v>
+        <v>0.36038505978024798</v>
       </c>
       <c r="Q18">
-        <v>0.3740881784816181</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
-        </is>
+        <v>0.37032900277356418</v>
+      </c>
+      <c r="R18">
+        <v>0.37464432429063721</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>35</v>
       </c>
       <c r="B19">
-        <v>0.3813235128307108</v>
+        <v>0.38214204584498229</v>
       </c>
       <c r="C19">
-        <v>0.4873828742199461</v>
+        <v>0.48594555921399668</v>
       </c>
       <c r="D19">
-        <v>0.5005927367964744</v>
+        <v>0.48720312438578028</v>
       </c>
       <c r="E19">
-        <v>0.5022179494868179</v>
+        <v>0.49977994028783218</v>
       </c>
       <c r="F19">
-        <v>0.5036944808147601</v>
+        <v>0.50359162197650531</v>
       </c>
       <c r="G19">
-        <v>0.4455717058626081</v>
+        <v>0.50506133861577363</v>
       </c>
       <c r="H19">
-        <v>0.4120866135415515</v>
+        <v>0.44852924319062187</v>
       </c>
       <c r="I19">
-        <v>0.3970714525506798</v>
+        <v>0.41251036484308828</v>
       </c>
       <c r="J19">
-        <v>0.374106803170845</v>
+        <v>0.3995381539033474</v>
       </c>
       <c r="K19">
-        <v>0.3594717395693051</v>
+        <v>0.37540463258144668</v>
       </c>
       <c r="L19">
-        <v>0.3528132882401501</v>
+        <v>0.36035302096348237</v>
       </c>
       <c r="M19">
-        <v>0.3462041634601196</v>
+        <v>0.35507456569155083</v>
       </c>
       <c r="N19">
-        <v>0.3446072759757995</v>
+        <v>0.34774889037667861</v>
       </c>
       <c r="O19">
-        <v>0.3465545984726394</v>
+        <v>0.34690132419107472</v>
       </c>
       <c r="P19">
-        <v>0.3450722449462176</v>
+        <v>0.34921365867251292</v>
       </c>
       <c r="Q19">
-        <v>0.34709552495685</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-        </is>
+        <v>0.34675497691429741</v>
+      </c>
+      <c r="R19">
+        <v>0.34876387694606992</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>36</v>
       </c>
       <c r="B20">
-        <v>0.380531065350338</v>
+        <v>0.37551046554323381</v>
       </c>
       <c r="C20">
-        <v>0.4870985003238467</v>
+        <v>0.48594555921399668</v>
       </c>
       <c r="D20">
-        <v>0.4939381314586508</v>
+        <v>0.48746894815545888</v>
       </c>
       <c r="E20">
-        <v>0.502408306709099</v>
+        <v>0.49731500890112551</v>
       </c>
       <c r="F20">
-        <v>0.479434785548053</v>
+        <v>0.50143733893693343</v>
       </c>
       <c r="G20">
-        <v>0.4387284146836714</v>
+        <v>0.47883892194393612</v>
       </c>
       <c r="H20">
-        <v>0.4309825990796646</v>
+        <v>0.43938253546396722</v>
       </c>
       <c r="I20">
-        <v>0.4031908148467622</v>
+        <v>0.43011875825750678</v>
       </c>
       <c r="J20">
-        <v>0.3808312038751483</v>
+        <v>0.4000811353698322</v>
       </c>
       <c r="K20">
-        <v>0.3689990874367589</v>
+        <v>0.37856017317553109</v>
       </c>
       <c r="L20">
-        <v>0.3541756965734822</v>
+        <v>0.3685543436191091</v>
       </c>
       <c r="M20">
-        <v>0.3479443586735576</v>
+        <v>0.35081711638328977</v>
       </c>
       <c r="N20">
-        <v>0.3522800974534042</v>
+        <v>0.34507386481663782</v>
       </c>
       <c r="O20">
-        <v>0.3354307254366742</v>
+        <v>0.35048610115543261</v>
       </c>
       <c r="P20">
-        <v>0.3370395213298006</v>
+        <v>0.33361650387502573</v>
       </c>
       <c r="Q20">
-        <v>0.3399389942229843</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.33635450068294293</v>
+      </c>
+      <c r="R20">
+        <v>0.3379979382747163</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>37</v>
       </c>
       <c r="B21">
-        <v>0.4419606725372274</v>
+        <v>0.43434065960212731</v>
       </c>
       <c r="C21">
-        <v>0.4863522624717752</v>
+        <v>0.48594555921399668</v>
       </c>
       <c r="D21">
-        <v>0.4905307788718875</v>
+        <v>0.48649930624382381</v>
       </c>
       <c r="E21">
-        <v>0.5167241929307235</v>
+        <v>0.4905968691329825</v>
       </c>
       <c r="F21">
-        <v>0.4784047765299551</v>
+        <v>0.51321579703134468</v>
       </c>
       <c r="G21">
-        <v>0.4589981984494294</v>
+        <v>0.47423506590125869</v>
       </c>
       <c r="H21">
-        <v>0.4498026655708093</v>
+        <v>0.45357315470192272</v>
       </c>
       <c r="I21">
-        <v>0.4380996006106974</v>
+        <v>0.44599359271177219</v>
       </c>
       <c r="J21">
-        <v>0.4273998237971877</v>
+        <v>0.43663237007772993</v>
       </c>
       <c r="K21">
-        <v>0.403722185703134</v>
+        <v>0.42347697862149491</v>
       </c>
       <c r="L21">
-        <v>0.3922910829762944</v>
+        <v>0.40317831663427439</v>
       </c>
       <c r="M21">
-        <v>0.3856632836119026</v>
+        <v>0.39230699758791338</v>
       </c>
       <c r="N21">
-        <v>0.3885977328076934</v>
+        <v>0.38547256273374109</v>
       </c>
       <c r="O21">
-        <v>0.395777892472686</v>
+        <v>0.3890510151476711</v>
       </c>
       <c r="P21">
-        <v>0.3989880345931693</v>
+        <v>0.39717891088670698</v>
       </c>
       <c r="Q21">
-        <v>0.3954382313900986</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.39925508125006859</v>
+      </c>
+      <c r="R21">
+        <v>0.39764975560799248</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>38</v>
       </c>
       <c r="B22">
-        <v>0.4500141918034271</v>
+        <v>0.45203959391939391</v>
       </c>
       <c r="C22">
-        <v>0.4866183042694504</v>
+        <v>0.48594555921399668</v>
       </c>
       <c r="D22">
-        <v>0.4910216876149196</v>
+        <v>0.48665555471799099</v>
       </c>
       <c r="E22">
-        <v>0.5153257585212354</v>
+        <v>0.491298054238268</v>
       </c>
       <c r="F22">
-        <v>0.4740853291069787</v>
+        <v>0.5139603526543699</v>
       </c>
       <c r="G22">
-        <v>0.4571411177737191</v>
+        <v>0.47349708993492601</v>
       </c>
       <c r="H22">
-        <v>0.4508773726581265</v>
+        <v>0.45659063054140231</v>
       </c>
       <c r="I22">
-        <v>0.4438702789084905</v>
+        <v>0.44982049643952893</v>
       </c>
       <c r="J22">
-        <v>0.4378541019943484</v>
+        <v>0.44216862645213351</v>
       </c>
       <c r="K22">
-        <v>0.4146713958577131</v>
+        <v>0.43551896080835151</v>
       </c>
       <c r="L22">
-        <v>0.4048542131521896</v>
+        <v>0.41380038501761712</v>
       </c>
       <c r="M22">
-        <v>0.4007235317243151</v>
+        <v>0.40276409165002558</v>
       </c>
       <c r="N22">
-        <v>0.3997205981117217</v>
+        <v>0.39690458016353419</v>
       </c>
       <c r="O22">
-        <v>0.402216684342632</v>
+        <v>0.39732490338402121</v>
       </c>
       <c r="P22">
-        <v>0.4030773149551162</v>
+        <v>0.40009442063896511</v>
       </c>
       <c r="Q22">
-        <v>0.4042788299557485</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.39994639267154147</v>
+      </c>
+      <c r="R22">
+        <v>0.40156531473617901</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>39</v>
       </c>
       <c r="B23">
-        <v>0.3853845899843697</v>
+        <v>0.38684311063141641</v>
       </c>
       <c r="C23">
-        <v>0.4860050112624487</v>
+        <v>0.48594555921399668</v>
       </c>
       <c r="D23">
-        <v>0.5020195437896152</v>
+        <v>0.48641006007626009</v>
       </c>
       <c r="E23">
-        <v>0.4656859507712289</v>
+        <v>0.50255194622171784</v>
       </c>
       <c r="F23">
-        <v>0.4522066390948386</v>
+        <v>0.46716517125688389</v>
       </c>
       <c r="G23">
-        <v>0.4058224783526301</v>
+        <v>0.45483476525401467</v>
       </c>
       <c r="H23">
-        <v>0.3795732597233188</v>
+        <v>0.4077453216677896</v>
       </c>
       <c r="I23">
-        <v>0.3674776685820385</v>
+        <v>0.38206011588720729</v>
       </c>
       <c r="J23">
-        <v>0.3575663147918921</v>
+        <v>0.37027111353144371</v>
       </c>
       <c r="K23">
-        <v>0.3495100905140385</v>
+        <v>0.36015452088274208</v>
       </c>
       <c r="L23">
-        <v>0.3489334340566729</v>
+        <v>0.35179268756629872</v>
       </c>
       <c r="M23">
-        <v>0.3499039166544538</v>
+        <v>0.34831477714526382</v>
       </c>
       <c r="N23">
-        <v>0.35802272891149</v>
+        <v>0.34807887759774098</v>
       </c>
       <c r="O23">
-        <v>0.3616511145743414</v>
+        <v>0.35524127854079218</v>
       </c>
       <c r="P23">
-        <v>0.3666934078192942</v>
+        <v>0.3611786889595503</v>
       </c>
       <c r="Q23">
-        <v>0.375016238805594</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.36678142781348722</v>
+      </c>
+      <c r="R23">
+        <v>0.37458118072150381</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>40</v>
       </c>
       <c r="B24">
-        <v>0.4978423131182571</v>
+        <v>0.45670108643464991</v>
       </c>
       <c r="C24">
-        <v>0.4978423131182571</v>
+        <v>0.48594555921399668</v>
       </c>
       <c r="D24">
-        <v>0.4824603984462625</v>
+        <v>0.49084085590133492</v>
       </c>
       <c r="E24">
-        <v>0.47762938126534</v>
+        <v>0.51345877487269043</v>
       </c>
       <c r="F24">
-        <v>0.4809584101053277</v>
+        <v>0.51721857221126921</v>
       </c>
       <c r="G24">
-        <v>0.4928166413780476</v>
+        <v>0.51077633512413068</v>
       </c>
       <c r="H24">
-        <v>0.5098086648174373</v>
+        <v>0.51221064385192561</v>
       </c>
       <c r="I24">
-        <v>0.5047640140015078</v>
+        <v>0.49557177641210631</v>
       </c>
       <c r="J24">
-        <v>0.5071160354003956</v>
+        <v>0.51067299154166479</v>
       </c>
       <c r="K24">
-        <v>0.524943542378501</v>
+        <v>0.48967582619882072</v>
       </c>
       <c r="L24">
-        <v>0.5555453688507769</v>
+        <v>0.44117349952279822</v>
       </c>
       <c r="M24">
-        <v>0.558348693592926</v>
+        <v>0.42342689939123779</v>
       </c>
       <c r="N24">
-        <v>0.5651959333115628</v>
+        <v>0.41325087404006111</v>
       </c>
       <c r="O24">
-        <v>0.5781902276298897</v>
+        <v>0.419353732307365</v>
       </c>
       <c r="P24">
-        <v>0.5910817280890365</v>
+        <v>0.4371730471141535</v>
       </c>
       <c r="Q24">
-        <v>0.6065679619946295</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.45040906262009389</v>
+      </c>
+      <c r="R24">
+        <v>0.46692033756607199</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>41</v>
       </c>
       <c r="B25">
-        <v>0.5400061297263863</v>
+        <v>0.46292553105899958</v>
       </c>
       <c r="C25">
-        <v>0.5400061297263863</v>
+        <v>0.48594555921399668</v>
       </c>
       <c r="D25">
-        <v>0.5176974169693979</v>
+        <v>0.4909172440776281</v>
       </c>
       <c r="E25">
-        <v>0.5066207708380001</v>
+        <v>0.51552829204001127</v>
       </c>
       <c r="F25">
-        <v>0.502232533088848</v>
+        <v>0.5170112988978578</v>
       </c>
       <c r="G25">
-        <v>0.5250453793664729</v>
+        <v>0.50825812721050745</v>
       </c>
       <c r="H25">
-        <v>0.5355596586858083</v>
+        <v>0.50728782560199037</v>
       </c>
       <c r="I25">
-        <v>0.5364424833389061</v>
+        <v>0.50363016532486304</v>
       </c>
       <c r="J25">
-        <v>0.5285316544662825</v>
+        <v>0.51989461052946928</v>
       </c>
       <c r="K25">
-        <v>0.5322059426600322</v>
+        <v>0.51009626442061784</v>
       </c>
       <c r="L25">
-        <v>0.5507607676111118</v>
+        <v>0.49013716119695527</v>
       </c>
       <c r="M25">
-        <v>0.5592124607173055</v>
+        <v>0.4360107644005235</v>
       </c>
       <c r="N25">
-        <v>0.581020006206845</v>
+        <v>0.42708482958390043</v>
       </c>
       <c r="O25">
-        <v>0.6001231398948311</v>
+        <v>0.41891227686980481</v>
       </c>
       <c r="P25">
-        <v>0.6095664191868998</v>
+        <v>0.42902420474469199</v>
       </c>
       <c r="Q25">
-        <v>0.6132506031004228</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.44214590277087018</v>
+      </c>
+      <c r="R25">
+        <v>0.45845970228363692</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>42</v>
       </c>
       <c r="B26">
-        <v>0.4988176487927437</v>
+        <v>0.4786279528763045</v>
       </c>
       <c r="C26">
-        <v>0.5012032770186075</v>
+        <v>0.48594555921399668</v>
       </c>
       <c r="D26">
-        <v>0.4798429185558821</v>
+        <v>0.4898144279153937</v>
       </c>
       <c r="E26">
-        <v>0.4717046016484175</v>
+        <v>0.51599420586704747</v>
       </c>
       <c r="F26">
-        <v>0.4642294226422148</v>
+        <v>0.51128512070217924</v>
       </c>
       <c r="G26">
-        <v>0.4653853967702961</v>
+        <v>0.50025646497664622</v>
       </c>
       <c r="H26">
-        <v>0.4556391795455395</v>
+        <v>0.50995449625790423</v>
       </c>
       <c r="I26">
-        <v>0.4528729688877901</v>
+        <v>0.50260912822016146</v>
       </c>
       <c r="J26">
-        <v>0.4538230290466383</v>
+        <v>0.47256909666798252</v>
       </c>
       <c r="K26">
-        <v>0.4495364792549903</v>
+        <v>0.48644632571732888</v>
       </c>
       <c r="L26">
-        <v>0.4469300419726782</v>
+        <v>0.45010823219807422</v>
       </c>
       <c r="M26">
-        <v>0.4542092334680851</v>
+        <v>0.42492224233635478</v>
       </c>
       <c r="N26">
-        <v>0.4584415089810182</v>
+        <v>0.42332909760507781</v>
       </c>
       <c r="O26">
-        <v>0.4665938574139014</v>
+        <v>0.43054999418000578</v>
       </c>
       <c r="P26">
-        <v>0.4748434404863817</v>
+        <v>0.44104811147467521</v>
       </c>
       <c r="Q26">
-        <v>0.4842263791264303</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.45416677251806759</v>
+      </c>
+      <c r="R26">
+        <v>0.47396244400570048</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>43</v>
       </c>
       <c r="B27">
-        <v>0.5050873180733021</v>
+        <v>0.43045241404720758</v>
       </c>
       <c r="C27">
-        <v>0.5058264414601903</v>
+        <v>0.48594555921399668</v>
       </c>
       <c r="D27">
-        <v>0.4873592267006607</v>
+        <v>0.49152318222970087</v>
       </c>
       <c r="E27">
-        <v>0.46351901511337</v>
+        <v>0.51712216160679403</v>
       </c>
       <c r="F27">
-        <v>0.4578405072043461</v>
+        <v>0.51199770028545044</v>
       </c>
       <c r="G27">
-        <v>0.4658069951709828</v>
+        <v>0.50245388225549292</v>
       </c>
       <c r="H27">
-        <v>0.4662308631257122</v>
+        <v>0.510174480100408</v>
       </c>
       <c r="I27">
-        <v>0.471158126002531</v>
+        <v>0.50353866348298382</v>
       </c>
       <c r="J27">
-        <v>0.4885591163703186</v>
+        <v>0.4772989297118666</v>
       </c>
       <c r="K27">
-        <v>0.4848687682911873</v>
+        <v>0.48742849737944832</v>
       </c>
       <c r="L27">
-        <v>0.4825092851938545</v>
+        <v>0.45489002696255909</v>
       </c>
       <c r="M27">
-        <v>0.4755360454325566</v>
+        <v>0.41344870113575238</v>
       </c>
       <c r="N27">
-        <v>0.4715224026794091</v>
+        <v>0.40339228042029618</v>
       </c>
       <c r="O27">
-        <v>0.4722925365233541</v>
+        <v>0.40133419542249538</v>
       </c>
       <c r="P27">
-        <v>0.4879046201749622</v>
+        <v>0.39838639721305152</v>
       </c>
       <c r="Q27">
-        <v>0.4990261585207267</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
-        </is>
+        <v>0.40433435816753999</v>
+      </c>
+      <c r="R27">
+        <v>0.40772676446344258</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>44</v>
       </c>
       <c r="B28">
-        <v>0.4611816079144779</v>
+        <v>0.43423574797661779</v>
       </c>
       <c r="C28">
-        <v>0.4901545718026233</v>
+        <v>0.48594555921399668</v>
       </c>
       <c r="D28">
-        <v>0.5135545097871825</v>
+        <v>0.49045831879986868</v>
       </c>
       <c r="E28">
-        <v>0.5176362121906282</v>
+        <v>0.513635414085997</v>
       </c>
       <c r="F28">
-        <v>0.5112205582268371</v>
+        <v>0.51589101565095041</v>
       </c>
       <c r="G28">
-        <v>0.5120750710295662</v>
+        <v>0.50726596908348853</v>
       </c>
       <c r="H28">
-        <v>0.4946521869599911</v>
+        <v>0.50594369030665443</v>
       </c>
       <c r="I28">
-        <v>0.5103948231306611</v>
+        <v>0.5013718557118596</v>
       </c>
       <c r="J28">
-        <v>0.4904331394058839</v>
+        <v>0.51309959035175345</v>
       </c>
       <c r="K28">
-        <v>0.4490031185425392</v>
+        <v>0.50727419780884797</v>
       </c>
       <c r="L28">
-        <v>0.4245446840308332</v>
+        <v>0.4892539073006138</v>
       </c>
       <c r="M28">
-        <v>0.4136891080601499</v>
+        <v>0.43155938203771321</v>
       </c>
       <c r="N28">
-        <v>0.4200336777160126</v>
+        <v>0.41582130500402043</v>
       </c>
       <c r="O28">
-        <v>0.438422053349179</v>
+        <v>0.41237240590702878</v>
       </c>
       <c r="P28">
-        <v>0.4509458610196682</v>
+        <v>0.41098568409237213</v>
       </c>
       <c r="Q28">
-        <v>0.470487522756556</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
-        </is>
+        <v>0.41686930362727281</v>
+      </c>
+      <c r="R28">
+        <v>0.41629913972875809</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>45</v>
       </c>
       <c r="B29">
-        <v>0.4623183628632481</v>
+        <v>0.42830593424911062</v>
       </c>
       <c r="C29">
-        <v>0.4910377906085563</v>
+        <v>0.48594555921399668</v>
       </c>
       <c r="D29">
-        <v>0.5155751683778349</v>
+        <v>0.49109875151938293</v>
       </c>
       <c r="E29">
-        <v>0.5174630230071732</v>
+        <v>0.51580068780360755</v>
       </c>
       <c r="F29">
-        <v>0.5089317776725171</v>
+        <v>0.51788896269479301</v>
       </c>
       <c r="G29">
-        <v>0.5074063609379756</v>
+        <v>0.51019934872703798</v>
       </c>
       <c r="H29">
-        <v>0.5027229321797058</v>
+        <v>0.50768941055962935</v>
       </c>
       <c r="I29">
-        <v>0.5197917636414702</v>
+        <v>0.50308242283971394</v>
       </c>
       <c r="J29">
-        <v>0.5041124239373004</v>
+        <v>0.51391605663294826</v>
       </c>
       <c r="K29">
-        <v>0.48561192477438</v>
+        <v>0.50914488190950336</v>
       </c>
       <c r="L29">
-        <v>0.4337143189706792</v>
+        <v>0.49254501416219909</v>
       </c>
       <c r="M29">
-        <v>0.4246344032075633</v>
+        <v>0.42740971677830891</v>
       </c>
       <c r="N29">
-        <v>0.4165586214431846</v>
+        <v>0.41211150955870213</v>
       </c>
       <c r="O29">
-        <v>0.4256422654163916</v>
+        <v>0.40467316118618352</v>
       </c>
       <c r="P29">
-        <v>0.4390886562362231</v>
+        <v>0.40242034631081619</v>
       </c>
       <c r="Q29">
-        <v>0.454468899977561</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
-        </is>
+        <v>0.40499617321696502</v>
+      </c>
+      <c r="R29">
+        <v>0.40270974325315562</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>46</v>
       </c>
       <c r="B30">
-        <v>0.4799749547767684</v>
+        <v>0.42836598283845218</v>
       </c>
       <c r="C30">
-        <v>0.4900729021036209</v>
+        <v>0.48594555921399668</v>
       </c>
       <c r="D30">
-        <v>0.5158256868850122</v>
+        <v>0.49056835026501422</v>
       </c>
       <c r="E30">
-        <v>0.5107391349332195</v>
+        <v>0.51470086938864601</v>
       </c>
       <c r="F30">
-        <v>0.5009925746156486</v>
+        <v>0.51761869495375812</v>
       </c>
       <c r="G30">
-        <v>0.5113830696088834</v>
+        <v>0.5095751340266671</v>
       </c>
       <c r="H30">
-        <v>0.5043360760127674</v>
+        <v>0.50843246116609753</v>
       </c>
       <c r="I30">
-        <v>0.4747242410588582</v>
+        <v>0.50282164538063201</v>
       </c>
       <c r="J30">
-        <v>0.4879629232024878</v>
+        <v>0.51704836713102298</v>
       </c>
       <c r="K30">
-        <v>0.4511334270840363</v>
+        <v>0.51268397971054358</v>
       </c>
       <c r="L30">
-        <v>0.4271685254268249</v>
+        <v>0.49585815305899078</v>
       </c>
       <c r="M30">
-        <v>0.4264703281042194</v>
+        <v>0.43037387782571401</v>
       </c>
       <c r="N30">
-        <v>0.4310901528120369</v>
+        <v>0.41562949455532727</v>
       </c>
       <c r="O30">
-        <v>0.4412636729011281</v>
+        <v>0.40870432100148019</v>
       </c>
       <c r="P30">
-        <v>0.455422284256189</v>
+        <v>0.40610755915014018</v>
       </c>
       <c r="Q30">
-        <v>0.4739368179348245</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-        </is>
+        <v>0.40607026527137008</v>
+      </c>
+      <c r="R30">
+        <v>0.40188037506755819</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>47</v>
       </c>
       <c r="B31">
-        <v>0.4281597031812618</v>
+        <v>0.43156295318636789</v>
       </c>
       <c r="C31">
-        <v>0.490940410980074</v>
+        <v>0.48594555921399668</v>
       </c>
       <c r="D31">
-        <v>0.5166683569286185</v>
+        <v>0.49153778706848872</v>
       </c>
       <c r="E31">
-        <v>0.5126193335921969</v>
+        <v>0.51511182289253643</v>
       </c>
       <c r="F31">
-        <v>0.5017736037805177</v>
+        <v>0.51706185718216091</v>
       </c>
       <c r="G31">
-        <v>0.5092970317446319</v>
+        <v>0.50895500715006758</v>
       </c>
       <c r="H31">
-        <v>0.5036323438783086</v>
+        <v>0.50720373751275649</v>
       </c>
       <c r="I31">
-        <v>0.4772822218018951</v>
+        <v>0.5015370170926623</v>
       </c>
       <c r="J31">
-        <v>0.4904221795594829</v>
+        <v>0.51327177177469507</v>
       </c>
       <c r="K31">
-        <v>0.4565045410959014</v>
+        <v>0.50896645114546035</v>
       </c>
       <c r="L31">
-        <v>0.4165571732455413</v>
+        <v>0.49240108883206429</v>
       </c>
       <c r="M31">
-        <v>0.4054870709790321</v>
+        <v>0.43184864312999821</v>
       </c>
       <c r="N31">
-        <v>0.4019139092367707</v>
+        <v>0.41531307485617819</v>
       </c>
       <c r="O31">
-        <v>0.4012109205952086</v>
+        <v>0.40832568516423928</v>
       </c>
       <c r="P31">
-        <v>0.4061890217436868</v>
+        <v>0.40284074076993243</v>
       </c>
       <c r="Q31">
-        <v>0.4088509540963157</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
-        </is>
+        <v>0.4047374832315439</v>
+      </c>
+      <c r="R31">
+        <v>0.39901834935250208</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>48</v>
       </c>
       <c r="B32">
-        <v>0.4386225962208765</v>
+        <v>0.44034820542876751</v>
       </c>
       <c r="C32">
-        <v>0.4903679302322791</v>
+        <v>0.48594555921399668</v>
       </c>
       <c r="D32">
-        <v>0.5144223501563832</v>
+        <v>0.49094532016184578</v>
       </c>
       <c r="E32">
-        <v>0.5171300727583678</v>
+        <v>0.51548311618794729</v>
       </c>
       <c r="F32">
-        <v>0.5089325954341146</v>
+        <v>0.51817797464646886</v>
       </c>
       <c r="G32">
-        <v>0.5068902984097564</v>
+        <v>0.51032694379816457</v>
       </c>
       <c r="H32">
-        <v>0.50283532315473</v>
+        <v>0.50806061535316327</v>
       </c>
       <c r="I32">
-        <v>0.5146607500882697</v>
+        <v>0.50237617463211603</v>
       </c>
       <c r="J32">
-        <v>0.5100030695525903</v>
+        <v>0.51703597477103735</v>
       </c>
       <c r="K32">
-        <v>0.4923000354501648</v>
+        <v>0.50590073542233382</v>
       </c>
       <c r="L32">
-        <v>0.43306770434676</v>
+        <v>0.48898233617644671</v>
       </c>
       <c r="M32">
-        <v>0.4143212570014371</v>
+        <v>0.43172607364412813</v>
       </c>
       <c r="N32">
-        <v>0.4101906717650063</v>
+        <v>0.41594602117936469</v>
       </c>
       <c r="O32">
-        <v>0.4075920741776709</v>
+        <v>0.40978096617440662</v>
       </c>
       <c r="P32">
-        <v>0.4141591631954395</v>
+        <v>0.41177486850295719</v>
       </c>
       <c r="Q32">
-        <v>0.4133968277919634</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
-        </is>
+        <v>0.42084939671058119</v>
+      </c>
+      <c r="R32">
+        <v>0.42450027034088672</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>49</v>
       </c>
       <c r="B33">
-        <v>0.4289303576738948</v>
+        <v>0.43564505322639019</v>
       </c>
       <c r="C33">
-        <v>0.4906279677614293</v>
+        <v>0.48594555921399668</v>
       </c>
       <c r="D33">
-        <v>0.5153321831238024</v>
+        <v>0.49124882340209602</v>
       </c>
       <c r="E33">
-        <v>0.5174477663450945</v>
+        <v>0.51663095758372679</v>
       </c>
       <c r="F33">
-        <v>0.5092104693496751</v>
+        <v>0.51958425520759977</v>
       </c>
       <c r="G33">
-        <v>0.5070246970796417</v>
+        <v>0.51123185443573149</v>
       </c>
       <c r="H33">
-        <v>0.5022071521565608</v>
+        <v>0.50839531697940454</v>
       </c>
       <c r="I33">
-        <v>0.514462699151768</v>
+        <v>0.50358748021699418</v>
       </c>
       <c r="J33">
-        <v>0.5079301845417151</v>
+        <v>0.51702983258543855</v>
       </c>
       <c r="K33">
-        <v>0.4912331540287647</v>
+        <v>0.50812362308011239</v>
       </c>
       <c r="L33">
-        <v>0.4261787508164412</v>
+        <v>0.49157923489052519</v>
       </c>
       <c r="M33">
-        <v>0.4114664937092318</v>
+        <v>0.42845460371542771</v>
       </c>
       <c r="N33">
-        <v>0.4063184102532829</v>
+        <v>0.41483293690998307</v>
       </c>
       <c r="O33">
-        <v>0.4031661219816582</v>
+        <v>0.40862003984777667</v>
       </c>
       <c r="P33">
-        <v>0.4049629353993432</v>
+        <v>0.41118011766856122</v>
       </c>
       <c r="Q33">
-        <v>0.4034411271217889</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
-        </is>
+        <v>0.41800496465750342</v>
+      </c>
+      <c r="R33">
+        <v>0.42282489638831022</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>50</v>
       </c>
       <c r="B34">
-        <v>0.4320080261363073</v>
+        <v>0.44445866963454728</v>
       </c>
       <c r="C34">
-        <v>0.4907224744673418</v>
+        <v>0.48594555921399668</v>
       </c>
       <c r="D34">
-        <v>0.5146483589432647</v>
+        <v>0.49122108915430251</v>
       </c>
       <c r="E34">
-        <v>0.5172244717361116</v>
+        <v>0.51564082080001061</v>
       </c>
       <c r="F34">
-        <v>0.5093589354243597</v>
+        <v>0.51854939250015686</v>
       </c>
       <c r="G34">
-        <v>0.5066089382450901</v>
+        <v>0.51074233321774987</v>
       </c>
       <c r="H34">
-        <v>0.5008891158522651</v>
+        <v>0.50842564910401666</v>
       </c>
       <c r="I34">
-        <v>0.5135355582791706</v>
+        <v>0.50238105602166994</v>
       </c>
       <c r="J34">
-        <v>0.510429131962103</v>
+        <v>0.51461215460054111</v>
       </c>
       <c r="K34">
-        <v>0.4933892852729858</v>
+        <v>0.50794795933492576</v>
       </c>
       <c r="L34">
-        <v>0.4287582224878047</v>
+        <v>0.49355031009859551</v>
       </c>
       <c r="M34">
-        <v>0.4149714511311657</v>
+        <v>0.43353772374017779</v>
       </c>
       <c r="N34">
-        <v>0.4092066966387115</v>
+        <v>0.41757527057124483</v>
       </c>
       <c r="O34">
-        <v>0.4092726505778744</v>
+        <v>0.40905687555455927</v>
       </c>
       <c r="P34">
-        <v>0.4080952127370809</v>
+        <v>0.40947671446480921</v>
       </c>
       <c r="Q34">
-        <v>0.4086659536083933</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
-        </is>
+        <v>0.41506095769804008</v>
+      </c>
+      <c r="R34">
+        <v>0.41669677844207609</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>51</v>
       </c>
       <c r="B35">
-        <v>0.4344004126913853</v>
+        <v>0.44212103897975419</v>
       </c>
       <c r="C35">
-        <v>0.4912016115656417</v>
+        <v>0.48594555921399668</v>
       </c>
       <c r="D35">
-        <v>0.5155795028610738</v>
+        <v>0.49071966734472511</v>
       </c>
       <c r="E35">
-        <v>0.5192002975394762</v>
+        <v>0.51541478831808318</v>
       </c>
       <c r="F35">
-        <v>0.5105924520528484</v>
+        <v>0.51811759739626917</v>
       </c>
       <c r="G35">
-        <v>0.5087207029467283</v>
+        <v>0.51035410029965267</v>
       </c>
       <c r="H35">
-        <v>0.5039908485223258</v>
+        <v>0.50903622376296542</v>
       </c>
       <c r="I35">
-        <v>0.5183371566615581</v>
+        <v>0.50344278242374108</v>
       </c>
       <c r="J35">
-        <v>0.5152410363441087</v>
+        <v>0.51451853342959897</v>
       </c>
       <c r="K35">
-        <v>0.499955713131003</v>
+        <v>0.50727257660921954</v>
       </c>
       <c r="L35">
-        <v>0.4364305711611154</v>
+        <v>0.49183082701209452</v>
       </c>
       <c r="M35">
-        <v>0.4211747536869107</v>
+        <v>0.42869847422318841</v>
       </c>
       <c r="N35">
-        <v>0.4127215614966557</v>
+        <v>0.41331945193115222</v>
       </c>
       <c r="O35">
-        <v>0.4074829120761207</v>
+        <v>0.40559842017559089</v>
       </c>
       <c r="P35">
-        <v>0.4087599644733571</v>
+        <v>0.4056074006080489</v>
       </c>
       <c r="Q35">
-        <v>0.4032297040340295</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-        </is>
+        <v>0.40979386839227427</v>
+      </c>
+      <c r="R35">
+        <v>0.41173949573377172</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>52</v>
       </c>
       <c r="B36">
-        <v>0.4488870253588377</v>
+        <v>0.4349566203011388</v>
       </c>
       <c r="C36">
-        <v>0.4913115845919304</v>
+        <v>0.48594555921399668</v>
       </c>
       <c r="D36">
-        <v>0.5164034999485476</v>
+        <v>0.49117238703708038</v>
       </c>
       <c r="E36">
-        <v>0.5188361490498071</v>
+        <v>0.51629998747460826</v>
       </c>
       <c r="F36">
-        <v>0.5101714312750559</v>
+        <v>0.51946627692433278</v>
       </c>
       <c r="G36">
-        <v>0.5090801840664879</v>
+        <v>0.51105221562021852</v>
       </c>
       <c r="H36">
-        <v>0.5044527602479003</v>
+        <v>0.50854461191671518</v>
       </c>
       <c r="I36">
-        <v>0.5171240850922505</v>
+        <v>0.50238405844104439</v>
       </c>
       <c r="J36">
-        <v>0.5105011734780546</v>
+        <v>0.51439617683401184</v>
       </c>
       <c r="K36">
-        <v>0.4930561364908898</v>
+        <v>0.50846279054444965</v>
       </c>
       <c r="L36">
-        <v>0.4330517845329634</v>
+        <v>0.49385402514583338</v>
       </c>
       <c r="M36">
-        <v>0.4152528996671885</v>
+        <v>0.43412631323835688</v>
       </c>
       <c r="N36">
-        <v>0.4078634525652465</v>
+        <v>0.41930163338938292</v>
       </c>
       <c r="O36">
-        <v>0.4111315971122282</v>
+        <v>0.40927828716210718</v>
       </c>
       <c r="P36">
-        <v>0.4195655964146631</v>
+        <v>0.40437924209511539</v>
       </c>
       <c r="Q36">
-        <v>0.4239378973405217</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
-        </is>
+        <v>0.4052297780432349</v>
+      </c>
+      <c r="R36">
+        <v>0.40022957155273781</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>53</v>
       </c>
       <c r="B37">
-        <v>0.4396520607456376</v>
+        <v>0.49782313095488639</v>
       </c>
       <c r="C37">
-        <v>0.4907839492586203</v>
+        <v>0.48594555921399668</v>
       </c>
       <c r="D37">
-        <v>0.5134493723240851</v>
+        <v>0.4919198086754264</v>
       </c>
       <c r="E37">
-        <v>0.5156923963200787</v>
+        <v>0.52190961635902278</v>
       </c>
       <c r="F37">
-        <v>0.5078151908424405</v>
+        <v>0.50898344348839064</v>
       </c>
       <c r="G37">
-        <v>0.5061404839936999</v>
+        <v>0.49776038660198918</v>
       </c>
       <c r="H37">
-        <v>0.500462331135655</v>
+        <v>0.50084029270245767</v>
       </c>
       <c r="I37">
-        <v>0.5140687016523952</v>
+        <v>0.49828410593836642</v>
       </c>
       <c r="J37">
-        <v>0.5078122188277238</v>
+        <v>0.47544934867927952</v>
       </c>
       <c r="K37">
-        <v>0.4906938124039997</v>
+        <v>0.47212695572113922</v>
       </c>
       <c r="L37">
-        <v>0.4321000567596132</v>
+        <v>0.47113862955828317</v>
       </c>
       <c r="M37">
-        <v>0.415287584251967</v>
+        <v>0.46510684027846633</v>
       </c>
       <c r="N37">
-        <v>0.4073292539337856</v>
+        <v>0.46793742549203171</v>
       </c>
       <c r="O37">
-        <v>0.4114355621102901</v>
+        <v>0.47701509017744198</v>
       </c>
       <c r="P37">
-        <v>0.4186998689878937</v>
+        <v>0.46750780612300252</v>
       </c>
       <c r="Q37">
-        <v>0.4227835561766074</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
-        </is>
+        <v>0.46148691751296589</v>
+      </c>
+      <c r="R37">
+        <v>0.45793509749039019</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>54</v>
       </c>
       <c r="B38">
-        <v>0.434463011577629</v>
+        <v>0.44703539543075949</v>
       </c>
       <c r="C38">
-        <v>0.4903284480513979</v>
+        <v>0.48594555921399668</v>
       </c>
       <c r="D38">
-        <v>0.5148174076965356</v>
+        <v>0.49140660858498891</v>
       </c>
       <c r="E38">
-        <v>0.5164383460800862</v>
+        <v>0.51724961450647533</v>
       </c>
       <c r="F38">
-        <v>0.5075482192621941</v>
+        <v>0.51122350542524009</v>
       </c>
       <c r="G38">
-        <v>0.5062017787803151</v>
+        <v>0.49096581673241729</v>
       </c>
       <c r="H38">
-        <v>0.5007651915645199</v>
+        <v>0.47443577002934012</v>
       </c>
       <c r="I38">
-        <v>0.5107376027277519</v>
+        <v>0.45091442582629798</v>
       </c>
       <c r="J38">
-        <v>0.5071314009604734</v>
+        <v>0.4136228713402178</v>
       </c>
       <c r="K38">
-        <v>0.491014098530089</v>
+        <v>0.41761538732219028</v>
       </c>
       <c r="L38">
-        <v>0.4306361298625336</v>
+        <v>0.42927386151298141</v>
       </c>
       <c r="M38">
-        <v>0.4156200397543156</v>
+        <v>0.43469465607819568</v>
       </c>
       <c r="N38">
-        <v>0.4092424058855842</v>
+        <v>0.43114313465675208</v>
       </c>
       <c r="O38">
-        <v>0.4089816624223877</v>
+        <v>0.42994224017711091</v>
       </c>
       <c r="P38">
-        <v>0.4130283335646277</v>
+        <v>0.42019082020596749</v>
       </c>
       <c r="Q38">
-        <v>0.416213021936542</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-        </is>
+        <v>0.41321159801345908</v>
+      </c>
+      <c r="R38">
+        <v>0.41173407890628588</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>55</v>
       </c>
       <c r="B39">
-        <v>0.442801214480904</v>
+        <v>0.44541558320593488</v>
       </c>
       <c r="C39">
-        <v>0.4912726948847585</v>
+        <v>0.48594555921399668</v>
       </c>
       <c r="D39">
-        <v>0.5156405536007076</v>
+        <v>0.49178728290194468</v>
       </c>
       <c r="E39">
-        <v>0.5177118820142909</v>
+        <v>0.51664599939489464</v>
       </c>
       <c r="F39">
-        <v>0.5095469707870496</v>
+        <v>0.50950185562830241</v>
       </c>
       <c r="G39">
-        <v>0.5066433611483705</v>
+        <v>0.48756013242173701</v>
       </c>
       <c r="H39">
-        <v>0.5020861995264393</v>
+        <v>0.47830999788559858</v>
       </c>
       <c r="I39">
-        <v>0.517158341536044</v>
+        <v>0.45683451518874008</v>
       </c>
       <c r="J39">
-        <v>0.5088482977620552</v>
+        <v>0.42258843917474131</v>
       </c>
       <c r="K39">
-        <v>0.4915255860956583</v>
+        <v>0.42122583718849732</v>
       </c>
       <c r="L39">
-        <v>0.4341614057188487</v>
+        <v>0.41724190607971978</v>
       </c>
       <c r="M39">
-        <v>0.4186004513305071</v>
+        <v>0.41643795231477992</v>
       </c>
       <c r="N39">
-        <v>0.4112328903304371</v>
+        <v>0.41540675938758798</v>
       </c>
       <c r="O39">
-        <v>0.4118124267041404</v>
+        <v>0.40598968838143951</v>
       </c>
       <c r="P39">
-        <v>0.4170865294193499</v>
+        <v>0.40456736366579787</v>
       </c>
       <c r="Q39">
-        <v>0.4190880015407247</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-        </is>
+        <v>0.40673163586730332</v>
+      </c>
+      <c r="R39">
+        <v>0.40433324580421642</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>56</v>
       </c>
       <c r="B40">
-        <v>0.4326412051433705</v>
+        <v>0.48743337502873452</v>
       </c>
       <c r="C40">
-        <v>0.4914679840479939</v>
+        <v>0.48594555921399668</v>
       </c>
       <c r="D40">
-        <v>0.5145031375959507</v>
+        <v>0.49632535162293528</v>
       </c>
       <c r="E40">
-        <v>0.5164567996098013</v>
+        <v>0.50040299419778711</v>
       </c>
       <c r="F40">
-        <v>0.5081236177675216</v>
+        <v>0.47916986986196419</v>
       </c>
       <c r="G40">
-        <v>0.5062949467376919</v>
+        <v>0.48831537854992157</v>
       </c>
       <c r="H40">
-        <v>0.5019757988356367</v>
+        <v>0.46082537880174362</v>
       </c>
       <c r="I40">
-        <v>0.5134278929027347</v>
+        <v>0.44389162383421532</v>
       </c>
       <c r="J40">
-        <v>0.5092435226983457</v>
+        <v>0.45251527608069569</v>
       </c>
       <c r="K40">
-        <v>0.493176179292135</v>
+        <v>0.46497635724029601</v>
       </c>
       <c r="L40">
-        <v>0.4321684981992661</v>
+        <v>0.46004473290108883</v>
       </c>
       <c r="M40">
-        <v>0.4179368629182468</v>
+        <v>0.4467327645774139</v>
       </c>
       <c r="N40">
-        <v>0.4105369878503089</v>
+        <v>0.44418617054271647</v>
       </c>
       <c r="O40">
-        <v>0.4057082337998271</v>
+        <v>0.43608835388039752</v>
       </c>
       <c r="P40">
-        <v>0.4075042371571334</v>
+        <v>0.43717019265143742</v>
       </c>
       <c r="Q40">
-        <v>0.4011991971017327</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.44579380711079591</v>
+      </c>
+      <c r="R40">
+        <v>0.46089319832122821</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>57</v>
       </c>
       <c r="B41">
-        <v>0.494874193620455</v>
+        <v>0.49527175250890521</v>
       </c>
       <c r="C41">
-        <v>0.4924203644872667</v>
+        <v>0.48594555921399668</v>
       </c>
       <c r="D41">
-        <v>0.5217934937190254</v>
+        <v>0.49511011312985459</v>
       </c>
       <c r="E41">
-        <v>0.5085114632571094</v>
+        <v>0.53416831469080583</v>
       </c>
       <c r="F41">
-        <v>0.5012347342924377</v>
+        <v>0.51722437984661973</v>
       </c>
       <c r="G41">
-        <v>0.5054749210965294</v>
+        <v>0.52785258040998762</v>
       </c>
       <c r="H41">
-        <v>0.5003411552269119</v>
+        <v>0.51179357880375043</v>
       </c>
       <c r="I41">
-        <v>0.4772035394544742</v>
+        <v>0.51066567259242179</v>
       </c>
       <c r="J41">
-        <v>0.4709760832453626</v>
+        <v>0.50238423777643104</v>
       </c>
       <c r="K41">
-        <v>0.4711726534683842</v>
+        <v>0.48401437857485963</v>
       </c>
       <c r="L41">
-        <v>0.4626838806591779</v>
+        <v>0.49353824638645799</v>
       </c>
       <c r="M41">
-        <v>0.4648881245063625</v>
+        <v>0.50009862705042774</v>
       </c>
       <c r="N41">
-        <v>0.4754947109413313</v>
+        <v>0.49808495445296741</v>
       </c>
       <c r="O41">
-        <v>0.4653813442918535</v>
+        <v>0.50500033943203682</v>
       </c>
       <c r="P41">
-        <v>0.4584350475648298</v>
+        <v>0.517845955471122</v>
       </c>
       <c r="Q41">
-        <v>0.4557029324461664</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
-        </is>
+        <v>0.51702940575244716</v>
+      </c>
+      <c r="R41">
+        <v>0.51893654189461158</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>58</v>
       </c>
       <c r="B42">
-        <v>0.4486062971985421</v>
+        <v>0.42253597756503952</v>
       </c>
       <c r="C42">
-        <v>0.4923577002975529</v>
+        <v>0.48594555921399668</v>
       </c>
       <c r="D42">
-        <v>0.5187770156792278</v>
+        <v>0.48600140502236799</v>
       </c>
       <c r="E42">
-        <v>0.5127085743676015</v>
+        <v>0.50661525757321746</v>
       </c>
       <c r="F42">
-        <v>0.489347394190875</v>
+        <v>0.53039151563451981</v>
       </c>
       <c r="G42">
-        <v>0.4727215960185741</v>
+        <v>0.47758224751983391</v>
       </c>
       <c r="H42">
-        <v>0.4486523919370021</v>
+        <v>0.44872758350825948</v>
       </c>
       <c r="I42">
-        <v>0.414883946780856</v>
+        <v>0.43577907553744633</v>
       </c>
       <c r="J42">
-        <v>0.4178581579349747</v>
+        <v>0.40125502026986731</v>
       </c>
       <c r="K42">
-        <v>0.4306067095756834</v>
+        <v>0.39894263342203851</v>
       </c>
       <c r="L42">
-        <v>0.436728734207043</v>
+        <v>0.40424457117904711</v>
       </c>
       <c r="M42">
-        <v>0.4360131279245923</v>
+        <v>0.38866201897263131</v>
       </c>
       <c r="N42">
-        <v>0.4322381550095653</v>
+        <v>0.38617695684920889</v>
       </c>
       <c r="O42">
-        <v>0.422187776107641</v>
+        <v>0.38965707784482789</v>
       </c>
       <c r="P42">
-        <v>0.4143047475534237</v>
+        <v>0.39216898820542812</v>
       </c>
       <c r="Q42">
-        <v>0.4126271847350352</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-        </is>
+        <v>0.39181191558158168</v>
+      </c>
+      <c r="R42">
+        <v>0.39575228446973609</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>59</v>
       </c>
       <c r="B43">
-        <v>0.4485102467968233</v>
+        <v>0.44851976172644958</v>
       </c>
       <c r="C43">
-        <v>0.4913558842646973</v>
+        <v>0.48594555921399668</v>
       </c>
       <c r="D43">
-        <v>0.5163582408469914</v>
+        <v>0.48815377260013287</v>
       </c>
       <c r="E43">
-        <v>0.5078525634525689</v>
+        <v>0.50599327566250929</v>
       </c>
       <c r="F43">
-        <v>0.4873444968869723</v>
+        <v>0.50092087399772034</v>
       </c>
       <c r="G43">
-        <v>0.4781244729908391</v>
+        <v>0.47241513008970509</v>
       </c>
       <c r="H43">
-        <v>0.455589227899151</v>
+        <v>0.43475859359608682</v>
       </c>
       <c r="I43">
-        <v>0.4231298551426253</v>
+        <v>0.42681391290918608</v>
       </c>
       <c r="J43">
-        <v>0.4197885992038056</v>
+        <v>0.41167163720432332</v>
       </c>
       <c r="K43">
-        <v>0.4204161604680247</v>
+        <v>0.4096004610723129</v>
       </c>
       <c r="L43">
-        <v>0.4186249741809022</v>
+        <v>0.41924294059576672</v>
       </c>
       <c r="M43">
-        <v>0.4193631958267206</v>
+        <v>0.41100971559088462</v>
       </c>
       <c r="N43">
-        <v>0.4099379532417916</v>
+        <v>0.40825337835860198</v>
       </c>
       <c r="O43">
-        <v>0.4068110020105177</v>
+        <v>0.41033959415354382</v>
       </c>
       <c r="P43">
-        <v>0.4067115409752927</v>
+        <v>0.4167864181533153</v>
       </c>
       <c r="Q43">
-        <v>0.4036817081875954</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
-        </is>
-      </c>
-      <c r="B44">
-        <v>0.4927869029834982</v>
-      </c>
-      <c r="C44">
-        <v>0.4993311404562504</v>
-      </c>
-      <c r="D44">
-        <v>0.5047517366411747</v>
-      </c>
-      <c r="E44">
-        <v>0.4809103946363611</v>
-      </c>
-      <c r="F44">
-        <v>0.4917456500384156</v>
-      </c>
-      <c r="G44">
-        <v>0.462858428706667</v>
-      </c>
-      <c r="H44">
-        <v>0.4445306379878873</v>
-      </c>
-      <c r="I44">
-        <v>0.4556310128060565</v>
-      </c>
-      <c r="J44">
-        <v>0.4681770311929872</v>
-      </c>
-      <c r="K44">
-        <v>0.4628268408235265</v>
-      </c>
-      <c r="L44">
-        <v>0.4500742666841356</v>
-      </c>
-      <c r="M44">
-        <v>0.447092571481614</v>
-      </c>
-      <c r="N44">
-        <v>0.4391842232802353</v>
-      </c>
-      <c r="O44">
-        <v>0.4411535179511162</v>
-      </c>
-      <c r="P44">
-        <v>0.4490677562247735</v>
-      </c>
-      <c r="Q44">
-        <v>0.4623199175892326</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>adj_snv_sder_c(1,3,5)_</t>
-        </is>
-      </c>
-      <c r="B45">
-        <v>0.4949621359408478</v>
-      </c>
-      <c r="C45">
-        <v>0.4943494887825846</v>
-      </c>
-      <c r="D45">
-        <v>0.5335507325477565</v>
-      </c>
-      <c r="E45">
-        <v>0.5155293781133745</v>
-      </c>
-      <c r="F45">
-        <v>0.5279636679966681</v>
-      </c>
-      <c r="G45">
-        <v>0.5108344547401212</v>
-      </c>
-      <c r="H45">
-        <v>0.5101213032292774</v>
-      </c>
-      <c r="I45">
-        <v>0.4990849112701474</v>
-      </c>
-      <c r="J45">
-        <v>0.4823831350295499</v>
-      </c>
-      <c r="K45">
-        <v>0.4915628989507057</v>
-      </c>
-      <c r="L45">
-        <v>0.4990324819854955</v>
-      </c>
-      <c r="M45">
-        <v>0.4955949313178721</v>
-      </c>
-      <c r="N45">
-        <v>0.5014116615635075</v>
-      </c>
-      <c r="O45">
-        <v>0.5138030477420222</v>
-      </c>
-      <c r="P45">
-        <v>0.513655309809165</v>
-      </c>
-      <c r="Q45">
-        <v>0.513943600520065</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>adj_snv_sder_c(2,3,15)_</t>
-        </is>
-      </c>
-      <c r="B46">
-        <v>0.4236746693200892</v>
-      </c>
-      <c r="C46">
-        <v>0.485675223519033</v>
-      </c>
-      <c r="D46">
-        <v>0.5037899180747631</v>
-      </c>
-      <c r="E46">
-        <v>0.5295479411049961</v>
-      </c>
-      <c r="F46">
-        <v>0.4727118470268732</v>
-      </c>
-      <c r="G46">
-        <v>0.4451079124710843</v>
-      </c>
-      <c r="H46">
-        <v>0.4353586767428674</v>
-      </c>
-      <c r="I46">
-        <v>0.3996078482817358</v>
-      </c>
-      <c r="J46">
-        <v>0.3987262880635674</v>
-      </c>
-      <c r="K46">
-        <v>0.4037779607698051</v>
-      </c>
-      <c r="L46">
-        <v>0.3896916986284102</v>
-      </c>
-      <c r="M46">
-        <v>0.3873490308958106</v>
-      </c>
-      <c r="N46">
-        <v>0.3902863868372032</v>
-      </c>
-      <c r="O46">
-        <v>0.3920645019299708</v>
-      </c>
-      <c r="P46">
-        <v>0.391690769676685</v>
-      </c>
-      <c r="Q46">
-        <v>0.3977673139452922</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
-        </is>
-      </c>
-      <c r="B47">
-        <v>0.4461287251535243</v>
-      </c>
-      <c r="C47">
-        <v>0.4879568783131614</v>
-      </c>
-      <c r="D47">
-        <v>0.5044568926765928</v>
-      </c>
-      <c r="E47">
-        <v>0.4998103560497642</v>
-      </c>
-      <c r="F47">
-        <v>0.4714453308058135</v>
-      </c>
-      <c r="G47">
-        <v>0.4344669798905135</v>
-      </c>
-      <c r="H47">
-        <v>0.4277669207017423</v>
-      </c>
-      <c r="I47">
-        <v>0.4118769404773597</v>
-      </c>
-      <c r="J47">
-        <v>0.408499247386427</v>
-      </c>
-      <c r="K47">
-        <v>0.4169786405412757</v>
-      </c>
-      <c r="L47">
-        <v>0.4112056673138204</v>
-      </c>
-      <c r="M47">
-        <v>0.4072445446686773</v>
-      </c>
-      <c r="N47">
-        <v>0.4090937610292969</v>
-      </c>
-      <c r="O47">
-        <v>0.4178812621640152</v>
-      </c>
-      <c r="P47">
-        <v>0.4249906681479446</v>
-      </c>
-      <c r="Q47">
-        <v>0.4324006526340856</v>
+        <v>0.42448042841323108</v>
+      </c>
+      <c r="R43">
+        <v>0.4295930515079418</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="C2:R43">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>